--- a/data/EMR with PPI Report-2026-07-01-15-08-38.xlsx
+++ b/data/EMR with PPI Report-2026-07-01-15-08-38.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADVAN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PEMROGRAMAN\LLM-DESKTOP\local-rag-comparator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C839AFD4-CDC5-4305-8CD4-732F7312043B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CD1419-FC6B-4CCA-A7F6-AE30AC2BFB6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8789" uniqueCount="1490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9356" uniqueCount="1608">
   <si>
     <t>EMR: EMR Name</t>
   </si>
@@ -4500,6 +4500,360 @@
   </si>
   <si>
     <t>Techcare.PPI.000289</t>
+  </si>
+  <si>
+    <t>PPI: Record ID</t>
+  </si>
+  <si>
+    <t>a1o2y000001L2WR</t>
+  </si>
+  <si>
+    <t>a1o2y000001L2Wb</t>
+  </si>
+  <si>
+    <t>a1o2y000003WRzZ</t>
+  </si>
+  <si>
+    <t>a1oIi000000CjX8</t>
+  </si>
+  <si>
+    <t>a1oIi000000CjYD</t>
+  </si>
+  <si>
+    <t>a1oIi000000CjYh</t>
+  </si>
+  <si>
+    <t>a1oIi000000ClrI</t>
+  </si>
+  <si>
+    <t>a1oIi000000CpgA</t>
+  </si>
+  <si>
+    <t>a1oIi000000Cphr</t>
+  </si>
+  <si>
+    <t>a1oIi000000Cpi6</t>
+  </si>
+  <si>
+    <t>a1oIi000000Ct3P</t>
+  </si>
+  <si>
+    <t>a1oIi000000DCj0</t>
+  </si>
+  <si>
+    <t>a1oIi000000DCj5</t>
+  </si>
+  <si>
+    <t>a1oIi000000DD5p</t>
+  </si>
+  <si>
+    <t>a1oIi000000DD6J</t>
+  </si>
+  <si>
+    <t>a1oIi000000DD9g</t>
+  </si>
+  <si>
+    <t>a1oIi000000DDAK</t>
+  </si>
+  <si>
+    <t>a1oIi000000DDDW</t>
+  </si>
+  <si>
+    <t>a1oMg000003PBbG</t>
+  </si>
+  <si>
+    <t>a1oMg000003PKRd</t>
+  </si>
+  <si>
+    <t>a1oMg000003PQLl</t>
+  </si>
+  <si>
+    <t>a1oMg000003PRV8</t>
+  </si>
+  <si>
+    <t>a1oMg000003Qz9N</t>
+  </si>
+  <si>
+    <t>a1oMg000003R3Mf</t>
+  </si>
+  <si>
+    <t>a1oMg000003RETc</t>
+  </si>
+  <si>
+    <t>a1oMg000003R8EN</t>
+  </si>
+  <si>
+    <t>a1oMg000003RGGh</t>
+  </si>
+  <si>
+    <t>a1oMg000003RYv7</t>
+  </si>
+  <si>
+    <t>a1oMg000003RV4V</t>
+  </si>
+  <si>
+    <t>a1oMg000003RcDx</t>
+  </si>
+  <si>
+    <t>a1oMg000003Rcys</t>
+  </si>
+  <si>
+    <t>a1oMg000003Vto5</t>
+  </si>
+  <si>
+    <t>a1oMg000003Vugv</t>
+  </si>
+  <si>
+    <t>a1oMg000003VvQ5</t>
+  </si>
+  <si>
+    <t>a1oMg000005Bbz5</t>
+  </si>
+  <si>
+    <t>a1oMg000008aGXt</t>
+  </si>
+  <si>
+    <t>a1oMg000009ejit</t>
+  </si>
+  <si>
+    <t>a1oMg00000BvCsX</t>
+  </si>
+  <si>
+    <t>a1oMg00000DzQhF</t>
+  </si>
+  <si>
+    <t>a1oMg00000H4Q73</t>
+  </si>
+  <si>
+    <t>a1oMg00000H4CQh</t>
+  </si>
+  <si>
+    <t>a1oMg00000Hb9KK</t>
+  </si>
+  <si>
+    <t>a1oMg00000IA6t1</t>
+  </si>
+  <si>
+    <t>a1oMg00000IHPyv</t>
+  </si>
+  <si>
+    <t>a1oMg00000Im3Ca</t>
+  </si>
+  <si>
+    <t>a1oMg00000Isgcc</t>
+  </si>
+  <si>
+    <t>a1oMg00000J0zjk</t>
+  </si>
+  <si>
+    <t>a1oMg00000J17Fr</t>
+  </si>
+  <si>
+    <t>a1oMg00000J29HB</t>
+  </si>
+  <si>
+    <t>a1oMg00000J5eev</t>
+  </si>
+  <si>
+    <t>a1oMg00000J67FB</t>
+  </si>
+  <si>
+    <t>a1oMg00000J7jtY</t>
+  </si>
+  <si>
+    <t>a1oMg00000J7wIr</t>
+  </si>
+  <si>
+    <t>a1oMg00000J82jF</t>
+  </si>
+  <si>
+    <t>a1oMg00000J87om</t>
+  </si>
+  <si>
+    <t>a1oMg00000J8d2r</t>
+  </si>
+  <si>
+    <t>a1oMg00000J82BQ</t>
+  </si>
+  <si>
+    <t>a1oMg00000J8ps1</t>
+  </si>
+  <si>
+    <t>a1oMg00000J8tPN</t>
+  </si>
+  <si>
+    <t>a1oMg00000J8baf</t>
+  </si>
+  <si>
+    <t>a1oMg00000J915B</t>
+  </si>
+  <si>
+    <t>a1oMg00000JCHNA</t>
+  </si>
+  <si>
+    <t>a1oMg00000JCWUD</t>
+  </si>
+  <si>
+    <t>a1oMg00000JCfvh</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDFUX</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDIyf</t>
+  </si>
+  <si>
+    <t>a1oMg00000JD0XD</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDoiP</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDpzU</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDsZ7</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDwCv</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDmqL</t>
+  </si>
+  <si>
+    <t>a1oMg00000JE2tR</t>
+  </si>
+  <si>
+    <t>a1oMg00000JE5kr</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDjMC</t>
+  </si>
+  <si>
+    <t>a1oMg00000JE4nF</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDymc</t>
+  </si>
+  <si>
+    <t>a1oMg00000JE1Ft</t>
+  </si>
+  <si>
+    <t>a1oMg00000JEHPR</t>
+  </si>
+  <si>
+    <t>a1oMg00000JEIer</t>
+  </si>
+  <si>
+    <t>a1oMg00000JDvdX</t>
+  </si>
+  <si>
+    <t>a1oMg00000JELpd</t>
+  </si>
+  <si>
+    <t>a1oMg00000JF3p6</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFCKT</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFJYr</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFLHJ</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFNEH</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFOK2</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFRTB</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFUFo</t>
+  </si>
+  <si>
+    <t>a1oMg00000JFWav</t>
+  </si>
+  <si>
+    <t>a1oMg00000JF8SA</t>
+  </si>
+  <si>
+    <t>a1oMg00000JU5aR</t>
+  </si>
+  <si>
+    <t>a1oMg00000JUMjR</t>
+  </si>
+  <si>
+    <t>a1oMg00000JUtoy</t>
+  </si>
+  <si>
+    <t>a1oMg00000JUoB3</t>
+  </si>
+  <si>
+    <t>a1oMg00000JVpL6</t>
+  </si>
+  <si>
+    <t>a1oMg00000JW23o</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWEMg</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWZ1M</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWbCq</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWZEE</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWd1k</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWhuv</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWfbP</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWkWE</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWe7W</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWn13</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWoMv</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWksq</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWkO8</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWrxV</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWtb7</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWv53</t>
+  </si>
+  <si>
+    <t>a1oMg00000JWvbJ</t>
+  </si>
+  <si>
+    <t>a1oMg00000RAuvx</t>
+  </si>
+  <si>
+    <t>a1oMg00000RBEPt</t>
   </si>
 </sst>
 </file>
@@ -4571,7 +4925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4584,6 +4938,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4898,7 +5253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R567"/>
+  <dimension ref="A1:S567"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4919,14 +5274,14 @@
     <col min="16" max="16" width="27" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
-    <col min="19" max="19" width="4.36328125" customWidth="1"/>
+    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="6"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4975,8 +5330,11 @@
       <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S1" s="4" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -5029,8 +5387,11 @@
       <c r="R2" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S2" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
@@ -5083,8 +5444,11 @@
       <c r="R3" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
@@ -5137,8 +5501,11 @@
       <c r="R4" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S4" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>36</v>
       </c>
@@ -5191,8 +5558,11 @@
       <c r="R5" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S5" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>37</v>
       </c>
@@ -5245,8 +5615,11 @@
       <c r="R6" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S6" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>38</v>
       </c>
@@ -5299,8 +5672,11 @@
       <c r="R7" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S7" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
@@ -5353,8 +5729,11 @@
       <c r="R8" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S8" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
@@ -5407,8 +5786,11 @@
       <c r="R9" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S9" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
@@ -5461,8 +5843,11 @@
       <c r="R10" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S10" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
@@ -5515,8 +5900,11 @@
       <c r="R11" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S11" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
@@ -5569,8 +5957,11 @@
       <c r="R12" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
@@ -5623,8 +6014,11 @@
       <c r="R13" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S13" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>45</v>
       </c>
@@ -5677,8 +6071,11 @@
       <c r="R14" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S14" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>46</v>
       </c>
@@ -5731,8 +6128,11 @@
       <c r="R15" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S15" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>47</v>
       </c>
@@ -5785,8 +6185,11 @@
       <c r="R16" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S16" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
@@ -5839,8 +6242,11 @@
       <c r="R17" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S17" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>49</v>
       </c>
@@ -5893,8 +6299,11 @@
       <c r="R18" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S18" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>50</v>
       </c>
@@ -5947,8 +6356,11 @@
       <c r="R19" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S19" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>51</v>
       </c>
@@ -6001,8 +6413,11 @@
       <c r="R20" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S20" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
@@ -6055,8 +6470,11 @@
       <c r="R21" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S21" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>53</v>
       </c>
@@ -6109,8 +6527,11 @@
       <c r="R22" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S22" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>54</v>
       </c>
@@ -6163,8 +6584,11 @@
       <c r="R23" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S23" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>68</v>
       </c>
@@ -6217,8 +6641,11 @@
       <c r="R24" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S24" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>69</v>
       </c>
@@ -6271,8 +6698,11 @@
       <c r="R25" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S25" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>70</v>
       </c>
@@ -6325,8 +6755,11 @@
       <c r="R26" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S26" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>71</v>
       </c>
@@ -6379,8 +6812,11 @@
       <c r="R27" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S27" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
@@ -6433,8 +6869,11 @@
       <c r="R28" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S28" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>73</v>
       </c>
@@ -6487,8 +6926,11 @@
       <c r="R29" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S29" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>74</v>
       </c>
@@ -6541,8 +6983,11 @@
       <c r="R30" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S30" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>75</v>
       </c>
@@ -6595,8 +7040,11 @@
       <c r="R31" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S31" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>91</v>
       </c>
@@ -6649,8 +7097,11 @@
       <c r="R32" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S32" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>92</v>
       </c>
@@ -6703,8 +7154,11 @@
       <c r="R33" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S33" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>93</v>
       </c>
@@ -6757,8 +7211,11 @@
       <c r="R34" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S34" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>94</v>
       </c>
@@ -6811,8 +7268,11 @@
       <c r="R35" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S35" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>95</v>
       </c>
@@ -6865,8 +7325,11 @@
       <c r="R36" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S36" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>96</v>
       </c>
@@ -6919,8 +7382,11 @@
       <c r="R37" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S37" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>109</v>
       </c>
@@ -6973,8 +7439,11 @@
       <c r="R38" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S38" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>110</v>
       </c>
@@ -7027,8 +7496,11 @@
       <c r="R39" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S39" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>123</v>
       </c>
@@ -7081,8 +7553,11 @@
       <c r="R40" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S40" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>124</v>
       </c>
@@ -7135,8 +7610,11 @@
       <c r="R41" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S41" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>125</v>
       </c>
@@ -7189,8 +7667,11 @@
       <c r="R42" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S42" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>126</v>
       </c>
@@ -7243,8 +7724,11 @@
       <c r="R43" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S43" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>127</v>
       </c>
@@ -7297,8 +7781,11 @@
       <c r="R44" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S44" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>128</v>
       </c>
@@ -7351,8 +7838,11 @@
       <c r="R45" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S45" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>129</v>
       </c>
@@ -7405,8 +7895,11 @@
       <c r="R46" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S46" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -7459,8 +7952,11 @@
       <c r="R47" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S47" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>144</v>
       </c>
@@ -7513,8 +8009,11 @@
       <c r="R48" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S48" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>145</v>
       </c>
@@ -7567,8 +8066,11 @@
       <c r="R49" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S49" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -7621,8 +8123,11 @@
       <c r="R50" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S50" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>147</v>
       </c>
@@ -7675,8 +8180,11 @@
       <c r="R51" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S51" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>159</v>
       </c>
@@ -7729,8 +8237,11 @@
       <c r="R52" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S52" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>160</v>
       </c>
@@ -7783,8 +8294,11 @@
       <c r="R53" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S53" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>161</v>
       </c>
@@ -7837,8 +8351,11 @@
       <c r="R54" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S54" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>162</v>
       </c>
@@ -7891,8 +8408,11 @@
       <c r="R55" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S55" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>163</v>
       </c>
@@ -7945,8 +8465,11 @@
       <c r="R56" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S56" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>164</v>
       </c>
@@ -7999,8 +8522,11 @@
       <c r="R57" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S57" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>165</v>
       </c>
@@ -8053,8 +8579,11 @@
       <c r="R58" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S58" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>166</v>
       </c>
@@ -8107,8 +8636,11 @@
       <c r="R59" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S59" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>167</v>
       </c>
@@ -8161,8 +8693,11 @@
       <c r="R60" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S60" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>168</v>
       </c>
@@ -8215,8 +8750,11 @@
       <c r="R61" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S61" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>169</v>
       </c>
@@ -8269,8 +8807,11 @@
       <c r="R62" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S62" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>170</v>
       </c>
@@ -8323,8 +8864,11 @@
       <c r="R63" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S63" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>171</v>
       </c>
@@ -8377,8 +8921,11 @@
       <c r="R64" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S64" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>172</v>
       </c>
@@ -8431,8 +8978,11 @@
       <c r="R65" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S65" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>173</v>
       </c>
@@ -8485,8 +9035,11 @@
       <c r="R66" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S66" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>174</v>
       </c>
@@ -8539,8 +9092,11 @@
       <c r="R67" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S67" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>175</v>
       </c>
@@ -8593,8 +9149,11 @@
       <c r="R68" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S68" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>176</v>
       </c>
@@ -8647,8 +9206,11 @@
       <c r="R69" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S69" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>177</v>
       </c>
@@ -8701,8 +9263,11 @@
       <c r="R70" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S70" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>178</v>
       </c>
@@ -8755,8 +9320,11 @@
       <c r="R71" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S71" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>179</v>
       </c>
@@ -8809,8 +9377,11 @@
       <c r="R72" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S72" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>180</v>
       </c>
@@ -8863,8 +9434,11 @@
       <c r="R73" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S73" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>181</v>
       </c>
@@ -8917,8 +9491,11 @@
       <c r="R74" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S74" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>182</v>
       </c>
@@ -8971,8 +9548,11 @@
       <c r="R75" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S75" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>183</v>
       </c>
@@ -9025,8 +9605,11 @@
       <c r="R76" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S76" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>184</v>
       </c>
@@ -9079,8 +9662,11 @@
       <c r="R77" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S77" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>185</v>
       </c>
@@ -9133,8 +9719,11 @@
       <c r="R78" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S78" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>186</v>
       </c>
@@ -9187,8 +9776,11 @@
       <c r="R79" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S79" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>187</v>
       </c>
@@ -9241,8 +9833,11 @@
       <c r="R80" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S80" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>188</v>
       </c>
@@ -9295,8 +9890,11 @@
       <c r="R81" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S81" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>189</v>
       </c>
@@ -9349,8 +9947,11 @@
       <c r="R82" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S82" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>190</v>
       </c>
@@ -9403,8 +10004,11 @@
       <c r="R83" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S83" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>191</v>
       </c>
@@ -9457,8 +10061,11 @@
       <c r="R84" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S84" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>192</v>
       </c>
@@ -9511,8 +10118,11 @@
       <c r="R85" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S85" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>193</v>
       </c>
@@ -9565,8 +10175,11 @@
       <c r="R86" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S86" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>194</v>
       </c>
@@ -9619,8 +10232,11 @@
       <c r="R87" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S87" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>195</v>
       </c>
@@ -9673,8 +10289,11 @@
       <c r="R88" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S88" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>196</v>
       </c>
@@ -9727,8 +10346,11 @@
       <c r="R89" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S89" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>197</v>
       </c>
@@ -9781,8 +10403,11 @@
       <c r="R90" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S90" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>198</v>
       </c>
@@ -9835,8 +10460,11 @@
       <c r="R91" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S91" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>199</v>
       </c>
@@ -9889,8 +10517,11 @@
       <c r="R92" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S92" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>200</v>
       </c>
@@ -9943,8 +10574,11 @@
       <c r="R93" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S93" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>201</v>
       </c>
@@ -9997,8 +10631,11 @@
       <c r="R94" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S94" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>202</v>
       </c>
@@ -10051,8 +10688,11 @@
       <c r="R95" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S95" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>203</v>
       </c>
@@ -10105,8 +10745,11 @@
       <c r="R96" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S96" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>204</v>
       </c>
@@ -10159,8 +10802,11 @@
       <c r="R97" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S97" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>205</v>
       </c>
@@ -10213,8 +10859,11 @@
       <c r="R98" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S98" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>206</v>
       </c>
@@ -10267,8 +10916,11 @@
       <c r="R99" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S99" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>207</v>
       </c>
@@ -10321,8 +10973,11 @@
       <c r="R100" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S100" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>208</v>
       </c>
@@ -10375,8 +11030,11 @@
       <c r="R101" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S101" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>209</v>
       </c>
@@ -10429,8 +11087,11 @@
       <c r="R102" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S102" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>210</v>
       </c>
@@ -10483,8 +11144,11 @@
       <c r="R103" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S103" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>211</v>
       </c>
@@ -10537,8 +11201,11 @@
       <c r="R104" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S104" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>225</v>
       </c>
@@ -10591,8 +11258,11 @@
       <c r="R105" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S105" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>226</v>
       </c>
@@ -10645,8 +11315,11 @@
       <c r="R106" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S106" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>227</v>
       </c>
@@ -10699,8 +11372,11 @@
       <c r="R107" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S107" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>240</v>
       </c>
@@ -10753,8 +11429,11 @@
       <c r="R108" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S108" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>241</v>
       </c>
@@ -10807,8 +11486,11 @@
       <c r="R109" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S109" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>242</v>
       </c>
@@ -10861,8 +11543,11 @@
       <c r="R110" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S110" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>243</v>
       </c>
@@ -10915,8 +11600,11 @@
       <c r="R111" s="2" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S111" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>257</v>
       </c>
@@ -10969,8 +11657,11 @@
       <c r="R112" s="2" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S112" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>258</v>
       </c>
@@ -11023,8 +11714,11 @@
       <c r="R113" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S113" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>272</v>
       </c>
@@ -11077,8 +11771,11 @@
       <c r="R114" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S114" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>273</v>
       </c>
@@ -11131,8 +11828,11 @@
       <c r="R115" s="2" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S115" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>284</v>
       </c>
@@ -11185,8 +11885,11 @@
       <c r="R116" s="2" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="117" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S116" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>295</v>
       </c>
@@ -11239,8 +11942,11 @@
       <c r="R117" s="2" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="118" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S117" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>296</v>
       </c>
@@ -11293,8 +11999,11 @@
       <c r="R118" s="2" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="119" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S118" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>297</v>
       </c>
@@ -11345,8 +12054,11 @@
       <c r="R119" s="2" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="120" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S119" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>309</v>
       </c>
@@ -11399,8 +12111,11 @@
       <c r="R120" s="2" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="121" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S120" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>319</v>
       </c>
@@ -11453,8 +12168,11 @@
       <c r="R121" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="122" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S121" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>329</v>
       </c>
@@ -11507,8 +12225,11 @@
       <c r="R122" s="2" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="123" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S122" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>340</v>
       </c>
@@ -11561,8 +12282,11 @@
       <c r="R123" s="2" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S123" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>341</v>
       </c>
@@ -11615,8 +12339,11 @@
       <c r="R124" s="2" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="125" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S124" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>342</v>
       </c>
@@ -11669,8 +12396,11 @@
       <c r="R125" s="2" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="126" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S125" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>354</v>
       </c>
@@ -11723,8 +12453,11 @@
       <c r="R126" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S126" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>366</v>
       </c>
@@ -11777,8 +12510,11 @@
       <c r="R127" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S127" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>367</v>
       </c>
@@ -11831,8 +12567,11 @@
       <c r="R128" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="129" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S128" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>368</v>
       </c>
@@ -11885,8 +12624,11 @@
       <c r="R129" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="130" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S129" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>369</v>
       </c>
@@ -11939,8 +12681,11 @@
       <c r="R130" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="131" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S130" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>370</v>
       </c>
@@ -11993,8 +12738,11 @@
       <c r="R131" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="132" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S131" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>371</v>
       </c>
@@ -12047,8 +12795,11 @@
       <c r="R132" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="133" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S132" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>372</v>
       </c>
@@ -12101,8 +12852,11 @@
       <c r="R133" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="134" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S133" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>387</v>
       </c>
@@ -12155,8 +12909,11 @@
       <c r="R134" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="135" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S134" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>388</v>
       </c>
@@ -12209,8 +12966,11 @@
       <c r="R135" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="136" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S135" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>389</v>
       </c>
@@ -12263,8 +13023,11 @@
       <c r="R136" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S136" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>390</v>
       </c>
@@ -12317,8 +13080,11 @@
       <c r="R137" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="138" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S137" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>391</v>
       </c>
@@ -12371,8 +13137,11 @@
       <c r="R138" s="2" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="139" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S138" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>392</v>
       </c>
@@ -12425,8 +13194,11 @@
       <c r="R139" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="140" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S139" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>404</v>
       </c>
@@ -12479,8 +13251,11 @@
       <c r="R140" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S140" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>405</v>
       </c>
@@ -12533,8 +13308,11 @@
       <c r="R141" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="142" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S141" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>406</v>
       </c>
@@ -12587,8 +13365,11 @@
       <c r="R142" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="143" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S142" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>407</v>
       </c>
@@ -12641,8 +13422,11 @@
       <c r="R143" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="144" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S143" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>408</v>
       </c>
@@ -12695,8 +13479,11 @@
       <c r="R144" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S144" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>409</v>
       </c>
@@ -12749,8 +13536,11 @@
       <c r="R145" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S145" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>410</v>
       </c>
@@ -12803,8 +13593,11 @@
       <c r="R146" s="2" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S146" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>411</v>
       </c>
@@ -12857,8 +13650,11 @@
       <c r="R147" s="2" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S147" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
         <v>424</v>
       </c>
@@ -12911,8 +13707,11 @@
       <c r="R148" s="2" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S148" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
         <v>435</v>
       </c>
@@ -12965,8 +13764,11 @@
       <c r="R149" s="2" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S149" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
         <v>448</v>
       </c>
@@ -13019,8 +13821,11 @@
       <c r="R150" s="2" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S150" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
         <v>458</v>
       </c>
@@ -13073,8 +13878,11 @@
       <c r="R151" s="2" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S151" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
         <v>465</v>
       </c>
@@ -13127,8 +13935,11 @@
       <c r="R152" s="2" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S152" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
         <v>475</v>
       </c>
@@ -13181,8 +13992,11 @@
       <c r="R153" s="2" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S153" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
         <v>485</v>
       </c>
@@ -13235,8 +14049,11 @@
       <c r="R154" s="2" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S154" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
         <v>486</v>
       </c>
@@ -13289,8 +14106,11 @@
       <c r="R155" s="2" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S155" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>487</v>
       </c>
@@ -13343,8 +14163,11 @@
       <c r="R156" s="2" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S156" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>501</v>
       </c>
@@ -13397,8 +14220,11 @@
       <c r="R157" s="2" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S157" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
         <v>513</v>
       </c>
@@ -13451,8 +14277,11 @@
       <c r="R158" s="2" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S158" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>524</v>
       </c>
@@ -13505,8 +14334,11 @@
       <c r="R159" s="2" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S159" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>537</v>
       </c>
@@ -13559,8 +14391,11 @@
       <c r="R160" s="2" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="161" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S160" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>538</v>
       </c>
@@ -13613,8 +14448,11 @@
       <c r="R161" s="2" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="162" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S161" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>548</v>
       </c>
@@ -13667,8 +14505,11 @@
       <c r="R162" s="2" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="163" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S162" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>549</v>
       </c>
@@ -13721,8 +14562,11 @@
       <c r="R163" s="2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S163" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
         <v>559</v>
       </c>
@@ -13771,8 +14615,11 @@
       <c r="R164" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="165" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S164" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>568</v>
       </c>
@@ -13821,8 +14668,11 @@
       <c r="R165" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="166" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S165" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>569</v>
       </c>
@@ -13871,8 +14721,11 @@
       <c r="R166" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="167" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S166" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>570</v>
       </c>
@@ -13921,8 +14774,11 @@
       <c r="R167" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="168" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S167" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>571</v>
       </c>
@@ -13971,8 +14827,11 @@
       <c r="R168" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="169" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S168" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>572</v>
       </c>
@@ -14021,8 +14880,11 @@
       <c r="R169" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="170" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S169" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>573</v>
       </c>
@@ -14071,8 +14933,11 @@
       <c r="R170" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="171" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S170" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>574</v>
       </c>
@@ -14121,8 +14986,11 @@
       <c r="R171" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="172" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S171" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>575</v>
       </c>
@@ -14171,8 +15039,11 @@
       <c r="R172" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="173" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S172" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
         <v>576</v>
       </c>
@@ -14221,8 +15092,11 @@
       <c r="R173" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="174" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S173" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>577</v>
       </c>
@@ -14271,8 +15145,11 @@
       <c r="R174" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="175" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S174" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>578</v>
       </c>
@@ -14321,8 +15198,11 @@
       <c r="R175" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="176" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S175" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
         <v>579</v>
       </c>
@@ -14371,8 +15251,11 @@
       <c r="R176" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="177" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S176" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>580</v>
       </c>
@@ -14421,8 +15304,11 @@
       <c r="R177" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="178" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S177" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>581</v>
       </c>
@@ -14471,8 +15357,11 @@
       <c r="R178" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="179" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S178" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
         <v>582</v>
       </c>
@@ -14521,8 +15410,11 @@
       <c r="R179" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="180" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S179" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
         <v>583</v>
       </c>
@@ -14571,8 +15463,11 @@
       <c r="R180" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="181" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S180" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
         <v>584</v>
       </c>
@@ -14621,8 +15516,11 @@
       <c r="R181" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S181" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
         <v>585</v>
       </c>
@@ -14671,8 +15569,11 @@
       <c r="R182" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="183" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S182" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>586</v>
       </c>
@@ -14721,8 +15622,11 @@
       <c r="R183" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="184" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S183" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>587</v>
       </c>
@@ -14771,8 +15675,11 @@
       <c r="R184" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="185" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S184" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>588</v>
       </c>
@@ -14821,8 +15728,11 @@
       <c r="R185" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="186" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S185" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>589</v>
       </c>
@@ -14871,8 +15781,11 @@
       <c r="R186" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="187" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S186" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
         <v>590</v>
       </c>
@@ -14921,8 +15834,11 @@
       <c r="R187" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="188" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S187" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>591</v>
       </c>
@@ -14971,8 +15887,11 @@
       <c r="R188" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="189" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S188" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
         <v>592</v>
       </c>
@@ -15021,8 +15940,11 @@
       <c r="R189" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="190" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S189" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
         <v>593</v>
       </c>
@@ -15071,8 +15993,11 @@
       <c r="R190" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="191" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S190" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
         <v>594</v>
       </c>
@@ -15121,8 +16046,11 @@
       <c r="R191" s="2" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="192" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S191" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
         <v>595</v>
       </c>
@@ -15175,8 +16103,11 @@
       <c r="R192" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="193" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S192" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
         <v>608</v>
       </c>
@@ -15229,8 +16160,11 @@
       <c r="R193" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="194" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S193" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
         <v>609</v>
       </c>
@@ -15283,8 +16217,11 @@
       <c r="R194" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="195" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S194" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
         <v>610</v>
       </c>
@@ -15337,8 +16274,11 @@
       <c r="R195" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="196" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S195" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
         <v>611</v>
       </c>
@@ -15391,8 +16331,11 @@
       <c r="R196" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="197" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S196" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
         <v>612</v>
       </c>
@@ -15445,8 +16388,11 @@
       <c r="R197" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="198" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S197" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="5" t="s">
         <v>613</v>
       </c>
@@ -15499,8 +16445,11 @@
       <c r="R198" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="199" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S198" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
         <v>614</v>
       </c>
@@ -15553,8 +16502,11 @@
       <c r="R199" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="200" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S199" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
         <v>615</v>
       </c>
@@ -15607,8 +16559,11 @@
       <c r="R200" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="201" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S200" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>616</v>
       </c>
@@ -15661,8 +16616,11 @@
       <c r="R201" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="202" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S201" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="5" t="s">
         <v>617</v>
       </c>
@@ -15715,8 +16673,11 @@
       <c r="R202" s="2" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="203" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S202" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
         <v>631</v>
       </c>
@@ -15763,8 +16724,11 @@
       <c r="R203" s="2" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="204" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S203" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="5" t="s">
         <v>640</v>
       </c>
@@ -15817,8 +16781,11 @@
       <c r="R204" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="205" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S204" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>651</v>
       </c>
@@ -15871,8 +16838,11 @@
       <c r="R205" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="206" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S205" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="5" t="s">
         <v>652</v>
       </c>
@@ -15925,8 +16895,11 @@
       <c r="R206" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="207" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S206" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
         <v>653</v>
       </c>
@@ -15979,8 +16952,11 @@
       <c r="R207" s="2" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="208" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S207" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
         <v>654</v>
       </c>
@@ -16033,8 +17009,11 @@
       <c r="R208" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="209" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S208" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>670</v>
       </c>
@@ -16087,8 +17066,11 @@
       <c r="R209" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="210" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S209" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
         <v>671</v>
       </c>
@@ -16141,8 +17123,11 @@
       <c r="R210" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="211" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S210" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
         <v>672</v>
       </c>
@@ -16195,8 +17180,11 @@
       <c r="R211" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="212" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S211" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>673</v>
       </c>
@@ -16249,8 +17237,11 @@
       <c r="R212" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="213" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S212" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
         <v>674</v>
       </c>
@@ -16303,8 +17294,11 @@
       <c r="R213" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="214" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S213" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="5" t="s">
         <v>675</v>
       </c>
@@ -16357,8 +17351,11 @@
       <c r="R214" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="215" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S214" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
         <v>676</v>
       </c>
@@ -16411,8 +17408,11 @@
       <c r="R215" s="2" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="216" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S215" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>677</v>
       </c>
@@ -16465,8 +17465,11 @@
       <c r="R216" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="217" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S216" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
         <v>684</v>
       </c>
@@ -16519,8 +17522,11 @@
       <c r="R217" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="218" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S217" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="5" t="s">
         <v>685</v>
       </c>
@@ -16573,8 +17579,11 @@
       <c r="R218" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="219" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S218" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
         <v>686</v>
       </c>
@@ -16627,8 +17636,11 @@
       <c r="R219" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="220" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S219" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="5" t="s">
         <v>687</v>
       </c>
@@ -16681,8 +17693,11 @@
       <c r="R220" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="221" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S220" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>688</v>
       </c>
@@ -16735,8 +17750,11 @@
       <c r="R221" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="222" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S221" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="5" t="s">
         <v>689</v>
       </c>
@@ -16789,8 +17807,11 @@
       <c r="R222" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="223" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S222" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
         <v>690</v>
       </c>
@@ -16843,8 +17864,11 @@
       <c r="R223" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="224" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S223" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="5" t="s">
         <v>691</v>
       </c>
@@ -16897,8 +17921,11 @@
       <c r="R224" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="225" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S224" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="5" t="s">
         <v>692</v>
       </c>
@@ -16951,8 +17978,11 @@
       <c r="R225" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="226" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S225" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="5" t="s">
         <v>693</v>
       </c>
@@ -17005,8 +18035,11 @@
       <c r="R226" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="227" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S226" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>694</v>
       </c>
@@ -17059,8 +18092,11 @@
       <c r="R227" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="228" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S227" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>695</v>
       </c>
@@ -17113,8 +18149,11 @@
       <c r="R228" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="229" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S228" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="5" t="s">
         <v>696</v>
       </c>
@@ -17167,8 +18206,11 @@
       <c r="R229" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="230" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S229" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="5" t="s">
         <v>697</v>
       </c>
@@ -17221,8 +18263,11 @@
       <c r="R230" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="231" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S230" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="5" t="s">
         <v>698</v>
       </c>
@@ -17275,8 +18320,11 @@
       <c r="R231" s="2" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="232" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S231" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="5" t="s">
         <v>699</v>
       </c>
@@ -17329,8 +18377,11 @@
       <c r="R232" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="233" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S232" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
         <v>710</v>
       </c>
@@ -17383,8 +18434,11 @@
       <c r="R233" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="234" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S233" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="5" t="s">
         <v>711</v>
       </c>
@@ -17437,8 +18491,11 @@
       <c r="R234" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="235" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S234" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
         <v>712</v>
       </c>
@@ -17491,8 +18548,11 @@
       <c r="R235" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="236" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S235" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="5" t="s">
         <v>713</v>
       </c>
@@ -17545,8 +18605,11 @@
       <c r="R236" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="237" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S236" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="5" t="s">
         <v>714</v>
       </c>
@@ -17599,8 +18662,11 @@
       <c r="R237" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="238" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S237" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>715</v>
       </c>
@@ -17653,8 +18719,11 @@
       <c r="R238" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="239" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S238" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="5" t="s">
         <v>716</v>
       </c>
@@ -17707,8 +18776,11 @@
       <c r="R239" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="240" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S239" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>717</v>
       </c>
@@ -17761,8 +18833,11 @@
       <c r="R240" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="241" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S240" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="5" t="s">
         <v>718</v>
       </c>
@@ -17815,8 +18890,11 @@
       <c r="R241" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="242" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S241" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="5" t="s">
         <v>719</v>
       </c>
@@ -17869,8 +18947,11 @@
       <c r="R242" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="243" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S242" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
         <v>720</v>
       </c>
@@ -17923,8 +19004,11 @@
       <c r="R243" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="244" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S243" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="5" t="s">
         <v>721</v>
       </c>
@@ -17977,8 +19061,11 @@
       <c r="R244" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="245" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S244" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
         <v>722</v>
       </c>
@@ -18031,8 +19118,11 @@
       <c r="R245" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="246" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S245" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="5" t="s">
         <v>723</v>
       </c>
@@ -18085,8 +19175,11 @@
       <c r="R246" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="247" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S246" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="5" t="s">
         <v>724</v>
       </c>
@@ -18139,8 +19232,11 @@
       <c r="R247" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="248" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S247" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>725</v>
       </c>
@@ -18193,8 +19289,11 @@
       <c r="R248" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="249" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S248" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="5" t="s">
         <v>726</v>
       </c>
@@ -18247,8 +19346,11 @@
       <c r="R249" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="250" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S249" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="5" t="s">
         <v>727</v>
       </c>
@@ -18301,8 +19403,11 @@
       <c r="R250" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="251" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S250" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="5" t="s">
         <v>728</v>
       </c>
@@ -18355,8 +19460,11 @@
       <c r="R251" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="252" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S251" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="5" t="s">
         <v>729</v>
       </c>
@@ -18409,8 +19517,11 @@
       <c r="R252" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="253" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S252" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>730</v>
       </c>
@@ -18463,8 +19574,11 @@
       <c r="R253" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="254" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S253" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="5" t="s">
         <v>731</v>
       </c>
@@ -18517,8 +19631,11 @@
       <c r="R254" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="255" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S254" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>732</v>
       </c>
@@ -18571,8 +19688,11 @@
       <c r="R255" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="256" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S255" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>733</v>
       </c>
@@ -18625,8 +19745,11 @@
       <c r="R256" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="257" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S256" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="5" t="s">
         <v>734</v>
       </c>
@@ -18679,8 +19802,11 @@
       <c r="R257" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="258" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S257" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="5" t="s">
         <v>735</v>
       </c>
@@ -18733,8 +19859,11 @@
       <c r="R258" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="259" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S258" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
         <v>736</v>
       </c>
@@ -18787,8 +19916,11 @@
       <c r="R259" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="260" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S259" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="5" t="s">
         <v>737</v>
       </c>
@@ -18841,8 +19973,11 @@
       <c r="R260" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="261" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S260" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>751</v>
       </c>
@@ -18895,8 +20030,11 @@
       <c r="R261" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="262" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S261" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="5" t="s">
         <v>752</v>
       </c>
@@ -18949,8 +20087,11 @@
       <c r="R262" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="263" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S262" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>753</v>
       </c>
@@ -19003,8 +20144,11 @@
       <c r="R263" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="264" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S263" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="5" t="s">
         <v>754</v>
       </c>
@@ -19057,8 +20201,11 @@
       <c r="R264" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="265" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S264" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>755</v>
       </c>
@@ -19111,8 +20258,11 @@
       <c r="R265" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="266" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S265" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="5" t="s">
         <v>756</v>
       </c>
@@ -19165,8 +20315,11 @@
       <c r="R266" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="267" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S266" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="5" t="s">
         <v>757</v>
       </c>
@@ -19219,8 +20372,11 @@
       <c r="R267" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="268" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S267" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" s="5" t="s">
         <v>758</v>
       </c>
@@ -19273,8 +20429,11 @@
       <c r="R268" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="269" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S268" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
         <v>759</v>
       </c>
@@ -19327,8 +20486,11 @@
       <c r="R269" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="270" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S269" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>760</v>
       </c>
@@ -19381,8 +20543,11 @@
       <c r="R270" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="271" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S270" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" s="5" t="s">
         <v>761</v>
       </c>
@@ -19435,8 +20600,11 @@
       <c r="R271" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="272" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S271" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" s="5" t="s">
         <v>762</v>
       </c>
@@ -19489,8 +20657,11 @@
       <c r="R272" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="273" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S272" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
         <v>763</v>
       </c>
@@ -19543,8 +20714,11 @@
       <c r="R273" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="274" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S273" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" s="5" t="s">
         <v>764</v>
       </c>
@@ -19597,8 +20771,11 @@
       <c r="R274" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="275" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S274" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" s="5" t="s">
         <v>765</v>
       </c>
@@ -19651,8 +20828,11 @@
       <c r="R275" s="2" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="276" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S275" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" s="5" t="s">
         <v>766</v>
       </c>
@@ -19705,8 +20885,11 @@
       <c r="R276" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="277" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S276" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
         <v>780</v>
       </c>
@@ -19759,8 +20942,11 @@
       <c r="R277" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="278" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S277" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="5" t="s">
         <v>781</v>
       </c>
@@ -19813,8 +20999,11 @@
       <c r="R278" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="279" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S278" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>782</v>
       </c>
@@ -19867,8 +21056,11 @@
       <c r="R279" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="280" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S279" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>783</v>
       </c>
@@ -19921,8 +21113,11 @@
       <c r="R280" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="281" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S280" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
         <v>784</v>
       </c>
@@ -19975,8 +21170,11 @@
       <c r="R281" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="282" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S281" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
         <v>785</v>
       </c>
@@ -20029,8 +21227,11 @@
       <c r="R282" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="283" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S282" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" s="5" t="s">
         <v>786</v>
       </c>
@@ -20083,8 +21284,11 @@
       <c r="R283" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="284" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S283" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" s="5" t="s">
         <v>787</v>
       </c>
@@ -20137,8 +21341,11 @@
       <c r="R284" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="285" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S284" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>788</v>
       </c>
@@ -20191,8 +21398,11 @@
       <c r="R285" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="286" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S285" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" s="5" t="s">
         <v>789</v>
       </c>
@@ -20245,8 +21455,11 @@
       <c r="R286" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="287" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S286" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" s="5" t="s">
         <v>790</v>
       </c>
@@ -20299,8 +21512,11 @@
       <c r="R287" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="288" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S287" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" s="5" t="s">
         <v>791</v>
       </c>
@@ -20353,8 +21569,11 @@
       <c r="R288" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="289" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S288" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>792</v>
       </c>
@@ -20407,8 +21626,11 @@
       <c r="R289" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="290" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S289" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" s="5" t="s">
         <v>806</v>
       </c>
@@ -20461,8 +21683,11 @@
       <c r="R290" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="291" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S290" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="5" t="s">
         <v>807</v>
       </c>
@@ -20515,8 +21740,11 @@
       <c r="R291" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="292" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S291" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" s="5" t="s">
         <v>808</v>
       </c>
@@ -20569,8 +21797,11 @@
       <c r="R292" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="293" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S292" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" s="5" t="s">
         <v>809</v>
       </c>
@@ -20623,8 +21854,11 @@
       <c r="R293" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="294" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S293" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" s="5" t="s">
         <v>810</v>
       </c>
@@ -20677,8 +21911,11 @@
       <c r="R294" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="295" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S294" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" s="5" t="s">
         <v>811</v>
       </c>
@@ -20731,8 +21968,11 @@
       <c r="R295" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="296" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S295" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" s="5" t="s">
         <v>812</v>
       </c>
@@ -20785,8 +22025,11 @@
       <c r="R296" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="297" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S296" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" s="5" t="s">
         <v>813</v>
       </c>
@@ -20839,8 +22082,11 @@
       <c r="R297" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="298" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S297" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" s="5" t="s">
         <v>814</v>
       </c>
@@ -20893,8 +22139,11 @@
       <c r="R298" s="2" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="299" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S298" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" s="5" t="s">
         <v>815</v>
       </c>
@@ -20947,8 +22196,11 @@
       <c r="R299" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="300" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S299" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" s="5" t="s">
         <v>827</v>
       </c>
@@ -21001,8 +22253,11 @@
       <c r="R300" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="301" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S300" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" s="5" t="s">
         <v>828</v>
       </c>
@@ -21055,8 +22310,11 @@
       <c r="R301" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="302" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S301" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" s="5" t="s">
         <v>829</v>
       </c>
@@ -21109,8 +22367,11 @@
       <c r="R302" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="303" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S302" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" s="5" t="s">
         <v>830</v>
       </c>
@@ -21163,8 +22424,11 @@
       <c r="R303" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="304" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S303" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" s="5" t="s">
         <v>831</v>
       </c>
@@ -21217,8 +22481,11 @@
       <c r="R304" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="305" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S304" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" s="5" t="s">
         <v>832</v>
       </c>
@@ -21271,8 +22538,11 @@
       <c r="R305" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="306" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S305" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" s="5" t="s">
         <v>833</v>
       </c>
@@ -21325,8 +22595,11 @@
       <c r="R306" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="307" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S306" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" s="5" t="s">
         <v>834</v>
       </c>
@@ -21379,8 +22652,11 @@
       <c r="R307" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="308" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S307" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" s="5" t="s">
         <v>835</v>
       </c>
@@ -21433,8 +22709,11 @@
       <c r="R308" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="309" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S308" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" s="5" t="s">
         <v>836</v>
       </c>
@@ -21487,8 +22766,11 @@
       <c r="R309" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="310" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S309" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" s="5" t="s">
         <v>837</v>
       </c>
@@ -21541,8 +22823,11 @@
       <c r="R310" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="311" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S310" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" s="5" t="s">
         <v>838</v>
       </c>
@@ -21595,8 +22880,11 @@
       <c r="R311" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="312" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S311" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" s="5" t="s">
         <v>839</v>
       </c>
@@ -21649,8 +22937,11 @@
       <c r="R312" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="313" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S312" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" s="5" t="s">
         <v>840</v>
       </c>
@@ -21703,8 +22994,11 @@
       <c r="R313" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="314" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S313" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" s="5" t="s">
         <v>841</v>
       </c>
@@ -21757,8 +23051,11 @@
       <c r="R314" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="315" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S314" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" s="5" t="s">
         <v>842</v>
       </c>
@@ -21811,8 +23108,11 @@
       <c r="R315" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="316" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S315" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" s="5" t="s">
         <v>843</v>
       </c>
@@ -21865,8 +23165,11 @@
       <c r="R316" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="317" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S316" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" s="5" t="s">
         <v>844</v>
       </c>
@@ -21919,8 +23222,11 @@
       <c r="R317" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="318" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S317" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" s="5" t="s">
         <v>845</v>
       </c>
@@ -21973,8 +23279,11 @@
       <c r="R318" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="319" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S318" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" s="5" t="s">
         <v>846</v>
       </c>
@@ -22027,8 +23336,11 @@
       <c r="R319" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="320" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S319" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" s="5" t="s">
         <v>847</v>
       </c>
@@ -22081,8 +23393,11 @@
       <c r="R320" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="321" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S320" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" s="5" t="s">
         <v>848</v>
       </c>
@@ -22135,8 +23450,11 @@
       <c r="R321" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="322" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S321" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" s="5" t="s">
         <v>849</v>
       </c>
@@ -22189,8 +23507,11 @@
       <c r="R322" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="323" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S322" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" s="5" t="s">
         <v>850</v>
       </c>
@@ -22243,8 +23564,11 @@
       <c r="R323" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="324" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S323" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" s="5" t="s">
         <v>851</v>
       </c>
@@ -22297,8 +23621,11 @@
       <c r="R324" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="325" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S324" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" s="5" t="s">
         <v>852</v>
       </c>
@@ -22351,8 +23678,11 @@
       <c r="R325" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="326" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S325" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" s="5" t="s">
         <v>853</v>
       </c>
@@ -22405,8 +23735,11 @@
       <c r="R326" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="327" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S326" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" s="5" t="s">
         <v>854</v>
       </c>
@@ -22459,8 +23792,11 @@
       <c r="R327" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="328" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S327" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" s="5" t="s">
         <v>855</v>
       </c>
@@ -22513,8 +23849,11 @@
       <c r="R328" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="329" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S328" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" s="5" t="s">
         <v>856</v>
       </c>
@@ -22567,8 +23906,11 @@
       <c r="R329" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="330" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S329" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" s="5" t="s">
         <v>857</v>
       </c>
@@ -22621,8 +23963,11 @@
       <c r="R330" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="331" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S330" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" s="5" t="s">
         <v>858</v>
       </c>
@@ -22675,8 +24020,11 @@
       <c r="R331" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="332" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S331" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" s="5" t="s">
         <v>859</v>
       </c>
@@ -22729,8 +24077,11 @@
       <c r="R332" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="333" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S332" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" s="5" t="s">
         <v>860</v>
       </c>
@@ -22783,8 +24134,11 @@
       <c r="R333" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="334" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S333" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" s="5" t="s">
         <v>861</v>
       </c>
@@ -22837,8 +24191,11 @@
       <c r="R334" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="335" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S334" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
         <v>862</v>
       </c>
@@ -22891,8 +24248,11 @@
       <c r="R335" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="336" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S335" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" s="5" t="s">
         <v>863</v>
       </c>
@@ -22945,8 +24305,11 @@
       <c r="R336" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="337" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S336" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" s="5" t="s">
         <v>864</v>
       </c>
@@ -22999,8 +24362,11 @@
       <c r="R337" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="338" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S337" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" s="5" t="s">
         <v>865</v>
       </c>
@@ -23053,8 +24419,11 @@
       <c r="R338" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="339" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S338" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" s="5" t="s">
         <v>866</v>
       </c>
@@ -23107,8 +24476,11 @@
       <c r="R339" s="2" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="340" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S339" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A340" s="5" t="s">
         <v>867</v>
       </c>
@@ -23161,8 +24533,11 @@
       <c r="R340" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="341" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S340" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A341" s="5" t="s">
         <v>879</v>
       </c>
@@ -23215,8 +24590,11 @@
       <c r="R341" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="342" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S341" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A342" s="5" t="s">
         <v>880</v>
       </c>
@@ -23269,8 +24647,11 @@
       <c r="R342" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="343" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S342" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A343" s="5" t="s">
         <v>881</v>
       </c>
@@ -23323,8 +24704,11 @@
       <c r="R343" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="344" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S343" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A344" s="5" t="s">
         <v>882</v>
       </c>
@@ -23377,8 +24761,11 @@
       <c r="R344" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="345" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S344" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A345" s="5" t="s">
         <v>883</v>
       </c>
@@ -23431,8 +24818,11 @@
       <c r="R345" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="346" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S345" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A346" s="5" t="s">
         <v>884</v>
       </c>
@@ -23485,8 +24875,11 @@
       <c r="R346" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="347" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S346" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A347" s="5" t="s">
         <v>885</v>
       </c>
@@ -23539,8 +24932,11 @@
       <c r="R347" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="348" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S347" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A348" s="5" t="s">
         <v>886</v>
       </c>
@@ -23593,8 +24989,11 @@
       <c r="R348" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="349" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S348" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A349" s="5" t="s">
         <v>887</v>
       </c>
@@ -23647,8 +25046,11 @@
       <c r="R349" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="350" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S349" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A350" s="5" t="s">
         <v>888</v>
       </c>
@@ -23701,8 +25103,11 @@
       <c r="R350" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="351" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S350" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A351" s="5" t="s">
         <v>889</v>
       </c>
@@ -23755,8 +25160,11 @@
       <c r="R351" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="352" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S351" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A352" s="5" t="s">
         <v>890</v>
       </c>
@@ -23809,8 +25217,11 @@
       <c r="R352" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="353" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S352" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
         <v>891</v>
       </c>
@@ -23863,8 +25274,11 @@
       <c r="R353" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="354" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S353" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A354" s="5" t="s">
         <v>892</v>
       </c>
@@ -23917,8 +25331,11 @@
       <c r="R354" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="355" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S354" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A355" s="5" t="s">
         <v>893</v>
       </c>
@@ -23971,8 +25388,11 @@
       <c r="R355" s="2" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="356" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S355" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="356" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A356" s="5" t="s">
         <v>894</v>
       </c>
@@ -24025,8 +25445,11 @@
       <c r="R356" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="357" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S356" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="357" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A357" s="5" t="s">
         <v>905</v>
       </c>
@@ -24079,8 +25502,11 @@
       <c r="R357" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="358" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S357" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="358" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A358" s="5" t="s">
         <v>906</v>
       </c>
@@ -24133,8 +25559,11 @@
       <c r="R358" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="359" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S358" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="359" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A359" s="5" t="s">
         <v>907</v>
       </c>
@@ -24187,8 +25616,11 @@
       <c r="R359" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="360" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S359" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="360" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A360" s="5" t="s">
         <v>908</v>
       </c>
@@ -24241,8 +25673,11 @@
       <c r="R360" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="361" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S360" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="361" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A361" s="5" t="s">
         <v>909</v>
       </c>
@@ -24295,8 +25730,11 @@
       <c r="R361" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="362" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S361" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="362" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A362" s="5" t="s">
         <v>910</v>
       </c>
@@ -24349,8 +25787,11 @@
       <c r="R362" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="363" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S362" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="363" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A363" s="5" t="s">
         <v>911</v>
       </c>
@@ -24403,8 +25844,11 @@
       <c r="R363" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="364" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S363" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A364" s="5" t="s">
         <v>912</v>
       </c>
@@ -24457,8 +25901,11 @@
       <c r="R364" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="365" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S364" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="365" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A365" s="5" t="s">
         <v>913</v>
       </c>
@@ -24511,8 +25958,11 @@
       <c r="R365" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="366" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S365" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A366" s="5" t="s">
         <v>914</v>
       </c>
@@ -24565,8 +26015,11 @@
       <c r="R366" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="367" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S366" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A367" s="5" t="s">
         <v>915</v>
       </c>
@@ -24619,8 +26072,11 @@
       <c r="R367" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="368" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S367" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A368" s="5" t="s">
         <v>916</v>
       </c>
@@ -24673,8 +26129,11 @@
       <c r="R368" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="369" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S368" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="369" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A369" s="5" t="s">
         <v>917</v>
       </c>
@@ -24727,8 +26186,11 @@
       <c r="R369" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="370" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S369" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="370" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A370" s="5" t="s">
         <v>918</v>
       </c>
@@ -24781,8 +26243,11 @@
       <c r="R370" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="371" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S370" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="371" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A371" s="5" t="s">
         <v>919</v>
       </c>
@@ -24835,8 +26300,11 @@
       <c r="R371" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="372" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S371" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="372" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A372" s="5" t="s">
         <v>920</v>
       </c>
@@ -24889,8 +26357,11 @@
       <c r="R372" s="2" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="373" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S372" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="373" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A373" s="5" t="s">
         <v>921</v>
       </c>
@@ -24943,8 +26414,11 @@
       <c r="R373" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="374" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S373" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="374" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A374" s="5" t="s">
         <v>933</v>
       </c>
@@ -24997,8 +26471,11 @@
       <c r="R374" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="375" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S374" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="375" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A375" s="5" t="s">
         <v>934</v>
       </c>
@@ -25051,8 +26528,11 @@
       <c r="R375" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="376" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S375" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="376" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A376" s="5" t="s">
         <v>935</v>
       </c>
@@ -25105,8 +26585,11 @@
       <c r="R376" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="377" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S376" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="377" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A377" s="5" t="s">
         <v>936</v>
       </c>
@@ -25159,8 +26642,11 @@
       <c r="R377" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="378" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S377" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="378" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A378" s="5" t="s">
         <v>937</v>
       </c>
@@ -25213,8 +26699,11 @@
       <c r="R378" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="379" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S378" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="379" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A379" s="5" t="s">
         <v>938</v>
       </c>
@@ -25267,8 +26756,11 @@
       <c r="R379" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="380" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S379" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="380" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A380" s="5" t="s">
         <v>939</v>
       </c>
@@ -25321,8 +26813,11 @@
       <c r="R380" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="381" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S380" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="381" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A381" s="5" t="s">
         <v>940</v>
       </c>
@@ -25375,8 +26870,11 @@
       <c r="R381" s="2" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="382" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S381" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="382" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A382" s="5" t="s">
         <v>941</v>
       </c>
@@ -25429,8 +26927,11 @@
       <c r="R382" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="383" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S382" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="383" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A383" s="5" t="s">
         <v>947</v>
       </c>
@@ -25483,8 +26984,11 @@
       <c r="R383" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="384" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S383" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="384" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A384" s="5" t="s">
         <v>948</v>
       </c>
@@ -25537,8 +27041,11 @@
       <c r="R384" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="385" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S384" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A385" s="5" t="s">
         <v>949</v>
       </c>
@@ -25591,8 +27098,11 @@
       <c r="R385" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="386" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S385" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A386" s="5" t="s">
         <v>950</v>
       </c>
@@ -25645,8 +27155,11 @@
       <c r="R386" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="387" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S386" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A387" s="5" t="s">
         <v>951</v>
       </c>
@@ -25699,8 +27212,11 @@
       <c r="R387" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="388" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S387" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A388" s="5" t="s">
         <v>952</v>
       </c>
@@ -25753,8 +27269,11 @@
       <c r="R388" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="389" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S388" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A389" s="5" t="s">
         <v>953</v>
       </c>
@@ -25807,8 +27326,11 @@
       <c r="R389" s="2" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="390" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S389" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A390" s="5" t="s">
         <v>954</v>
       </c>
@@ -25859,8 +27381,11 @@
       <c r="R390" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="391" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S390" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A391" s="5" t="s">
         <v>966</v>
       </c>
@@ -25911,8 +27436,11 @@
       <c r="R391" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="392" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S391" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A392" s="5" t="s">
         <v>967</v>
       </c>
@@ -25963,8 +27491,11 @@
       <c r="R392" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="393" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S392" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A393" s="5" t="s">
         <v>968</v>
       </c>
@@ -26015,8 +27546,11 @@
       <c r="R393" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="394" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S393" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A394" s="5" t="s">
         <v>969</v>
       </c>
@@ -26067,8 +27601,11 @@
       <c r="R394" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="395" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S394" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A395" s="5" t="s">
         <v>970</v>
       </c>
@@ -26119,8 +27656,11 @@
       <c r="R395" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="396" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S395" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A396" s="5" t="s">
         <v>971</v>
       </c>
@@ -26171,8 +27711,11 @@
       <c r="R396" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="397" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S396" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A397" s="5" t="s">
         <v>972</v>
       </c>
@@ -26223,8 +27766,11 @@
       <c r="R397" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="398" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S397" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A398" s="5" t="s">
         <v>973</v>
       </c>
@@ -26275,8 +27821,11 @@
       <c r="R398" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="399" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S398" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A399" s="5" t="s">
         <v>974</v>
       </c>
@@ -26327,8 +27876,11 @@
       <c r="R399" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="400" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S399" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A400" s="5" t="s">
         <v>975</v>
       </c>
@@ -26379,8 +27931,11 @@
       <c r="R400" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="401" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S400" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A401" s="5" t="s">
         <v>976</v>
       </c>
@@ -26431,8 +27986,11 @@
       <c r="R401" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="402" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S401" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A402" s="5" t="s">
         <v>977</v>
       </c>
@@ -26483,8 +28041,11 @@
       <c r="R402" s="2" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="403" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S402" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A403" s="5" t="s">
         <v>978</v>
       </c>
@@ -26527,8 +28088,11 @@
       <c r="R403" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="404" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S403" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A404" s="5" t="s">
         <v>984</v>
       </c>
@@ -26571,8 +28135,11 @@
       <c r="R404" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="405" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S404" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A405" s="5" t="s">
         <v>985</v>
       </c>
@@ -26615,8 +28182,11 @@
       <c r="R405" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="406" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S405" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A406" s="5" t="s">
         <v>986</v>
       </c>
@@ -26659,8 +28229,11 @@
       <c r="R406" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="407" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S406" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A407" s="5" t="s">
         <v>987</v>
       </c>
@@ -26703,8 +28276,11 @@
       <c r="R407" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="408" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S407" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A408" s="5" t="s">
         <v>988</v>
       </c>
@@ -26747,8 +28323,11 @@
       <c r="R408" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="409" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S408" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A409" s="5" t="s">
         <v>989</v>
       </c>
@@ -26791,8 +28370,11 @@
       <c r="R409" s="2" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="410" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S409" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A410" s="5" t="s">
         <v>990</v>
       </c>
@@ -26835,8 +28417,11 @@
       <c r="R410" s="2" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="411" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S410" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A411" s="5" t="s">
         <v>994</v>
       </c>
@@ -26879,8 +28464,11 @@
       <c r="R411" s="2" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="412" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S411" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A412" s="5" t="s">
         <v>995</v>
       </c>
@@ -26923,8 +28511,11 @@
       <c r="R412" s="2" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="413" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S412" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A413" s="5" t="s">
         <v>996</v>
       </c>
@@ -26967,8 +28558,11 @@
       <c r="R413" s="2" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="414" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S413" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A414" s="5" t="s">
         <v>997</v>
       </c>
@@ -27011,8 +28605,11 @@
       <c r="R414" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="415" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S414" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A415" s="5" t="s">
         <v>1005</v>
       </c>
@@ -27055,8 +28652,11 @@
       <c r="R415" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="416" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S415" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="416" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A416" s="5" t="s">
         <v>1006</v>
       </c>
@@ -27099,8 +28699,11 @@
       <c r="R416" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="417" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S416" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="417" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A417" s="5" t="s">
         <v>1007</v>
       </c>
@@ -27143,8 +28746,11 @@
       <c r="R417" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="418" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S417" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="418" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A418" s="5" t="s">
         <v>1008</v>
       </c>
@@ -27187,8 +28793,11 @@
       <c r="R418" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="419" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S418" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="419" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A419" s="5" t="s">
         <v>1009</v>
       </c>
@@ -27231,8 +28840,11 @@
       <c r="R419" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="420" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S419" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="420" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A420" s="5" t="s">
         <v>1010</v>
       </c>
@@ -27275,8 +28887,11 @@
       <c r="R420" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="421" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S420" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="421" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A421" s="5" t="s">
         <v>1011</v>
       </c>
@@ -27319,8 +28934,11 @@
       <c r="R421" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="422" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S421" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="422" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A422" s="5" t="s">
         <v>1012</v>
       </c>
@@ -27363,8 +28981,11 @@
       <c r="R422" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="423" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S422" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="423" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A423" s="5" t="s">
         <v>1013</v>
       </c>
@@ -27407,8 +29028,11 @@
       <c r="R423" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="424" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S423" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="424" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A424" s="5" t="s">
         <v>1014</v>
       </c>
@@ -27451,8 +29075,11 @@
       <c r="R424" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="425" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S424" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="425" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A425" s="5" t="s">
         <v>1015</v>
       </c>
@@ -27495,8 +29122,11 @@
       <c r="R425" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="426" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S425" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="426" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A426" s="5" t="s">
         <v>1016</v>
       </c>
@@ -27539,8 +29169,11 @@
       <c r="R426" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="427" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S426" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="427" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A427" s="5" t="s">
         <v>1017</v>
       </c>
@@ -27583,8 +29216,11 @@
       <c r="R427" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="428" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S427" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="428" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A428" s="5" t="s">
         <v>1018</v>
       </c>
@@ -27627,8 +29263,11 @@
       <c r="R428" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="429" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S428" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="429" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A429" s="5" t="s">
         <v>1019</v>
       </c>
@@ -27671,8 +29310,11 @@
       <c r="R429" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="430" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S429" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="430" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A430" s="5" t="s">
         <v>1020</v>
       </c>
@@ -27715,8 +29357,11 @@
       <c r="R430" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="431" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S430" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="431" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A431" s="5" t="s">
         <v>1021</v>
       </c>
@@ -27759,8 +29404,11 @@
       <c r="R431" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="432" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S431" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="432" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A432" s="5" t="s">
         <v>1022</v>
       </c>
@@ -27803,8 +29451,11 @@
       <c r="R432" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="433" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S432" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="433" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A433" s="5" t="s">
         <v>1023</v>
       </c>
@@ -27847,8 +29498,11 @@
       <c r="R433" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="434" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S433" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="434" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A434" s="5" t="s">
         <v>1024</v>
       </c>
@@ -27891,8 +29545,11 @@
       <c r="R434" s="2" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="435" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S434" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="435" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A435" s="5" t="s">
         <v>1029</v>
       </c>
@@ -27935,8 +29592,11 @@
       <c r="R435" s="2" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="436" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S435" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="436" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A436" s="5" t="s">
         <v>1030</v>
       </c>
@@ -27979,8 +29639,11 @@
       <c r="R436" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="437" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S436" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A437" s="5" t="s">
         <v>1037</v>
       </c>
@@ -28023,8 +29686,11 @@
       <c r="R437" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="438" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S437" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A438" s="5" t="s">
         <v>1038</v>
       </c>
@@ -28067,8 +29733,11 @@
       <c r="R438" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="439" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S438" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="439" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A439" s="5" t="s">
         <v>1039</v>
       </c>
@@ -28111,8 +29780,11 @@
       <c r="R439" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="440" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S439" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A440" s="5" t="s">
         <v>1040</v>
       </c>
@@ -28155,8 +29827,11 @@
       <c r="R440" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="441" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S440" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="441" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A441" s="5" t="s">
         <v>1041</v>
       </c>
@@ -28199,8 +29874,11 @@
       <c r="R441" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="442" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S441" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="442" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A442" s="5" t="s">
         <v>1042</v>
       </c>
@@ -28243,8 +29921,11 @@
       <c r="R442" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="443" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S442" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="443" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A443" s="5" t="s">
         <v>1043</v>
       </c>
@@ -28287,8 +29968,11 @@
       <c r="R443" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="444" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S443" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="444" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A444" s="5" t="s">
         <v>1044</v>
       </c>
@@ -28331,8 +30015,11 @@
       <c r="R444" s="2" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="445" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S444" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="445" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A445" s="5" t="s">
         <v>1045</v>
       </c>
@@ -28375,8 +30062,11 @@
       <c r="R445" s="2" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="446" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S445" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="446" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A446" s="5" t="s">
         <v>1051</v>
       </c>
@@ -28419,8 +30109,11 @@
       <c r="R446" s="2" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="447" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S446" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="447" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A447" s="5" t="s">
         <v>1052</v>
       </c>
@@ -28463,8 +30156,11 @@
       <c r="R447" s="2" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="448" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S447" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="448" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A448" s="5" t="s">
         <v>1053</v>
       </c>
@@ -28507,8 +30203,11 @@
       <c r="R448" s="2" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="449" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S448" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="449" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A449" s="5" t="s">
         <v>1054</v>
       </c>
@@ -28551,8 +30250,11 @@
       <c r="R449" s="2" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="450" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S449" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="450" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A450" s="5" t="s">
         <v>1058</v>
       </c>
@@ -28595,8 +30297,11 @@
       <c r="R450" s="2" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="451" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S450" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="451" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A451" s="5" t="s">
         <v>1059</v>
       </c>
@@ -28641,8 +30346,11 @@
       <c r="R451" s="2" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="452" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S451" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="452" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A452" s="5" t="s">
         <v>1066</v>
       </c>
@@ -28687,8 +30395,11 @@
       <c r="R452" s="2" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="453" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S452" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="453" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A453" s="5" t="s">
         <v>1067</v>
       </c>
@@ -28733,8 +30444,11 @@
       <c r="R453" s="2" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="454" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S453" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="454" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A454" s="5" t="s">
         <v>1068</v>
       </c>
@@ -28787,8 +30501,11 @@
       <c r="R454" s="2" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="455" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S454" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="455" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A455" s="5" t="s">
         <v>1079</v>
       </c>
@@ -28841,8 +30558,11 @@
       <c r="R455" s="2" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="456" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S455" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="456" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A456" s="5" t="s">
         <v>1080</v>
       </c>
@@ -28895,8 +30615,11 @@
       <c r="R456" s="2" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="457" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S456" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="457" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A457" s="5" t="s">
         <v>1081</v>
       </c>
@@ -28949,8 +30672,11 @@
       <c r="R457" s="2" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="458" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S457" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="458" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A458" s="5" t="s">
         <v>1082</v>
       </c>
@@ -29003,8 +30729,11 @@
       <c r="R458" s="2" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="459" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S458" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="459" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A459" s="5" t="s">
         <v>1083</v>
       </c>
@@ -29047,8 +30776,11 @@
       <c r="R459" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="460" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S459" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="460" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A460" s="5" t="s">
         <v>1089</v>
       </c>
@@ -29091,8 +30823,11 @@
       <c r="R460" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="461" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S460" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="461" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A461" s="5" t="s">
         <v>1090</v>
       </c>
@@ -29135,8 +30870,11 @@
       <c r="R461" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="462" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S461" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="462" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A462" s="5" t="s">
         <v>1091</v>
       </c>
@@ -29179,8 +30917,11 @@
       <c r="R462" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="463" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S462" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="463" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A463" s="5" t="s">
         <v>1092</v>
       </c>
@@ -29223,8 +30964,11 @@
       <c r="R463" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="464" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S463" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="464" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A464" s="5" t="s">
         <v>1093</v>
       </c>
@@ -29267,8 +31011,11 @@
       <c r="R464" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="465" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S464" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="465" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A465" s="5" t="s">
         <v>1094</v>
       </c>
@@ -29311,8 +31058,11 @@
       <c r="R465" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="466" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S465" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="466" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A466" s="5" t="s">
         <v>1095</v>
       </c>
@@ -29355,8 +31105,11 @@
       <c r="R466" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="467" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S466" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="467" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A467" s="5" t="s">
         <v>1096</v>
       </c>
@@ -29399,8 +31152,11 @@
       <c r="R467" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="468" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S467" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="468" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A468" s="5" t="s">
         <v>1097</v>
       </c>
@@ -29443,8 +31199,11 @@
       <c r="R468" s="2" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="469" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S468" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="469" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A469" s="5" t="s">
         <v>1098</v>
       </c>
@@ -29487,8 +31246,11 @@
       <c r="R469" s="2" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="470" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S469" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="470" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A470" s="5" t="s">
         <v>1105</v>
       </c>
@@ -29531,8 +31293,11 @@
       <c r="R470" s="2" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="471" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S470" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="471" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A471" s="5" t="s">
         <v>1106</v>
       </c>
@@ -29575,8 +31340,11 @@
       <c r="R471" s="2" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="472" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S471" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="472" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A472" s="5" t="s">
         <v>1107</v>
       </c>
@@ -29619,8 +31387,11 @@
       <c r="R472" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="473" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S472" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="473" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A473" s="5" t="s">
         <v>1114</v>
       </c>
@@ -29663,8 +31434,11 @@
       <c r="R473" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="474" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S473" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="474" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A474" s="5" t="s">
         <v>1115</v>
       </c>
@@ -29707,8 +31481,11 @@
       <c r="R474" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="475" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S474" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="475" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A475" s="5" t="s">
         <v>1116</v>
       </c>
@@ -29751,8 +31528,11 @@
       <c r="R475" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="476" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S475" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="476" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A476" s="5" t="s">
         <v>1117</v>
       </c>
@@ -29795,8 +31575,11 @@
       <c r="R476" s="2" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="477" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S476" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="477" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A477" s="5" t="s">
         <v>1125</v>
       </c>
@@ -29839,8 +31622,11 @@
       <c r="R477" s="2" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="478" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S477" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="478" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A478" s="5" t="s">
         <v>1126</v>
       </c>
@@ -29883,8 +31669,11 @@
       <c r="R478" s="2" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="479" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S478" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="479" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A479" s="5" t="s">
         <v>1127</v>
       </c>
@@ -29927,8 +31716,11 @@
       <c r="R479" s="2" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="480" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S479" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="480" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A480" s="5" t="s">
         <v>1134</v>
       </c>
@@ -29971,8 +31763,11 @@
       <c r="R480" s="2" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="481" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S480" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="481" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A481" s="5" t="s">
         <v>1141</v>
       </c>
@@ -30015,8 +31810,11 @@
       <c r="R481" s="2" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="482" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S481" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="482" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A482" s="5" t="s">
         <v>1142</v>
       </c>
@@ -30059,8 +31857,11 @@
       <c r="R482" s="2" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="483" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S482" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="483" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A483" s="5" t="s">
         <v>1147</v>
       </c>
@@ -30103,8 +31904,11 @@
       <c r="R483" s="2" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="484" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S483" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="484" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A484" s="5" t="s">
         <v>1148</v>
       </c>
@@ -30147,8 +31951,11 @@
       <c r="R484" s="2" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="485" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S484" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="485" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A485" s="5" t="s">
         <v>1155</v>
       </c>
@@ -30191,8 +31998,11 @@
       <c r="R485" s="2" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="486" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S485" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="486" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A486" s="5" t="s">
         <v>1156</v>
       </c>
@@ -30235,8 +32045,11 @@
       <c r="R486" s="2" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="487" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S486" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="487" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A487" s="5" t="s">
         <v>1163</v>
       </c>
@@ -30279,8 +32092,11 @@
       <c r="R487" s="2" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="488" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S487" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="488" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A488" s="5" t="s">
         <v>1164</v>
       </c>
@@ -30323,8 +32139,11 @@
       <c r="R488" s="2" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="489" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S488" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="489" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A489" s="5" t="s">
         <v>1165</v>
       </c>
@@ -30367,8 +32186,11 @@
       <c r="R489" s="2" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="490" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S489" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="490" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A490" s="5" t="s">
         <v>1172</v>
       </c>
@@ -30411,8 +32233,11 @@
       <c r="R490" s="2" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="491" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S490" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="491" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A491" s="5" t="s">
         <v>1173</v>
       </c>
@@ -30455,8 +32280,11 @@
       <c r="R491" s="2" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="492" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S491" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="492" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A492" s="5" t="s">
         <v>1179</v>
       </c>
@@ -30499,8 +32327,11 @@
       <c r="R492" s="2" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="493" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S492" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="493" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A493" s="5" t="s">
         <v>1180</v>
       </c>
@@ -30543,8 +32374,11 @@
       <c r="R493" s="2" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="494" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S493" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="494" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A494" s="5" t="s">
         <v>1181</v>
       </c>
@@ -30587,8 +32421,11 @@
       <c r="R494" s="2" t="s">
         <v>1178</v>
       </c>
-    </row>
-    <row r="495" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S494" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="495" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A495" s="5" t="s">
         <v>1182</v>
       </c>
@@ -30631,8 +32468,11 @@
       <c r="R495" s="2" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="496" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S495" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="496" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A496" s="5" t="s">
         <v>1187</v>
       </c>
@@ -30675,8 +32515,11 @@
       <c r="R496" s="2" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="497" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S496" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="497" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A497" s="5" t="s">
         <v>1188</v>
       </c>
@@ -30719,8 +32562,11 @@
       <c r="R497" s="2" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="498" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S497" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="498" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A498" s="5" t="s">
         <v>1189</v>
       </c>
@@ -30763,8 +32609,11 @@
       <c r="R498" s="2" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="499" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S498" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="499" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A499" s="5" t="s">
         <v>1197</v>
       </c>
@@ -30807,8 +32656,11 @@
       <c r="R499" s="2" t="s">
         <v>1203</v>
       </c>
-    </row>
-    <row r="500" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S499" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="500" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A500" s="5" t="s">
         <v>1204</v>
       </c>
@@ -30851,8 +32703,11 @@
       <c r="R500" s="2" t="s">
         <v>1203</v>
       </c>
-    </row>
-    <row r="501" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S500" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="501" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A501" s="5" t="s">
         <v>1205</v>
       </c>
@@ -30895,8 +32750,11 @@
       <c r="R501" s="2" t="s">
         <v>1211</v>
       </c>
-    </row>
-    <row r="502" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S501" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="502" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A502" s="5" t="s">
         <v>1212</v>
       </c>
@@ -30939,8 +32797,11 @@
       <c r="R502" s="2" t="s">
         <v>1211</v>
       </c>
-    </row>
-    <row r="503" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S502" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="503" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A503" s="5" t="s">
         <v>1213</v>
       </c>
@@ -30983,8 +32844,11 @@
       <c r="R503" s="2" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="504" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S503" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="504" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A504" s="5" t="s">
         <v>1218</v>
       </c>
@@ -31027,8 +32891,11 @@
       <c r="R504" s="2" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="505" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S504" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="505" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A505" s="5" t="s">
         <v>1219</v>
       </c>
@@ -31071,8 +32938,11 @@
       <c r="R505" s="2" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="506" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S505" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="506" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A506" s="5" t="s">
         <v>1225</v>
       </c>
@@ -31115,8 +32985,11 @@
       <c r="R506" s="2" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="507" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S506" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="507" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A507" s="5" t="s">
         <v>1226</v>
       </c>
@@ -31159,8 +33032,11 @@
       <c r="R507" s="2" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="508" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S507" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="508" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A508" s="5" t="s">
         <v>1227</v>
       </c>
@@ -31203,8 +33079,11 @@
       <c r="R508" s="2" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="509" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S508" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="509" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A509" s="5" t="s">
         <v>1228</v>
       </c>
@@ -31247,8 +33126,11 @@
       <c r="R509" s="2" t="s">
         <v>1234</v>
       </c>
-    </row>
-    <row r="510" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S509" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="510" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A510" s="5" t="s">
         <v>1235</v>
       </c>
@@ -31291,8 +33173,11 @@
       <c r="R510" s="2" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="511" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S510" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="511" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A511" s="5" t="s">
         <v>1241</v>
       </c>
@@ -31335,8 +33220,11 @@
       <c r="R511" s="2" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="512" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S511" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="512" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A512" s="5" t="s">
         <v>1242</v>
       </c>
@@ -31379,8 +33267,11 @@
       <c r="R512" s="2" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="513" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S512" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="513" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A513" s="5" t="s">
         <v>1249</v>
       </c>
@@ -31423,8 +33314,11 @@
       <c r="R513" s="2" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="514" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S513" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="514" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A514" s="5" t="s">
         <v>1255</v>
       </c>
@@ -31467,8 +33361,11 @@
       <c r="R514" s="2" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="515" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S514" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="515" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A515" s="5" t="s">
         <v>1261</v>
       </c>
@@ -31511,8 +33408,11 @@
       <c r="R515" s="2" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="516" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S515" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="516" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A516" s="5" t="s">
         <v>1262</v>
       </c>
@@ -31555,8 +33455,11 @@
       <c r="R516" s="2" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="517" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S516" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="517" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A517" s="5" t="s">
         <v>1263</v>
       </c>
@@ -31599,8 +33502,11 @@
       <c r="R517" s="2" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="518" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S517" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="518" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A518" s="5" t="s">
         <v>1264</v>
       </c>
@@ -31643,8 +33549,11 @@
       <c r="R518" s="2" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="519" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S518" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="519" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A519" s="5" t="s">
         <v>1265</v>
       </c>
@@ -31687,8 +33596,11 @@
       <c r="R519" s="2" t="s">
         <v>1270</v>
       </c>
-    </row>
-    <row r="520" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S519" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="520" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A520" s="5" t="s">
         <v>1271</v>
       </c>
@@ -31731,8 +33643,11 @@
       <c r="R520" s="2" t="s">
         <v>1277</v>
       </c>
-    </row>
-    <row r="521" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S520" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="521" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A521" s="5" t="s">
         <v>1278</v>
       </c>
@@ -31775,8 +33690,11 @@
       <c r="R521" s="2" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="522" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S521" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="522" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A522" s="5" t="s">
         <v>1283</v>
       </c>
@@ -31819,8 +33737,11 @@
       <c r="R522" s="2" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="523" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S522" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="523" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A523" s="5" t="s">
         <v>1284</v>
       </c>
@@ -31863,8 +33784,11 @@
       <c r="R523" s="2" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="524" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S523" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="524" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A524" s="5" t="s">
         <v>1285</v>
       </c>
@@ -31907,8 +33831,11 @@
       <c r="R524" s="2" t="s">
         <v>1291</v>
       </c>
-    </row>
-    <row r="525" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S524" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="525" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A525" s="5" t="s">
         <v>1292</v>
       </c>
@@ -31951,8 +33878,11 @@
       <c r="R525" s="2" t="s">
         <v>1296</v>
       </c>
-    </row>
-    <row r="526" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S525" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="526" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A526" s="5" t="s">
         <v>1297</v>
       </c>
@@ -31995,8 +33925,11 @@
       <c r="R526" s="2" t="s">
         <v>1296</v>
       </c>
-    </row>
-    <row r="527" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S526" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="527" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A527" s="5" t="s">
         <v>1298</v>
       </c>
@@ -32039,8 +33972,11 @@
       <c r="R527" s="2" t="s">
         <v>1303</v>
       </c>
-    </row>
-    <row r="528" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S527" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="528" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A528" s="5" t="s">
         <v>1304</v>
       </c>
@@ -32083,8 +34019,11 @@
       <c r="R528" s="2" t="s">
         <v>1309</v>
       </c>
-    </row>
-    <row r="529" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S528" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A529" s="5" t="s">
         <v>1310</v>
       </c>
@@ -32127,8 +34066,11 @@
       <c r="R529" s="2" t="s">
         <v>1315</v>
       </c>
-    </row>
-    <row r="530" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S529" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="530" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A530" s="5" t="s">
         <v>1316</v>
       </c>
@@ -32171,8 +34113,11 @@
       <c r="R530" s="2" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="531" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S530" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="531" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A531" s="5" t="s">
         <v>1322</v>
       </c>
@@ -32215,8 +34160,11 @@
       <c r="R531" s="2" t="s">
         <v>1327</v>
       </c>
-    </row>
-    <row r="532" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S531" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="532" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A532" s="5" t="s">
         <v>1328</v>
       </c>
@@ -32259,8 +34207,11 @@
       <c r="R532" s="2" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="533" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S532" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="533" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A533" s="5" t="s">
         <v>1334</v>
       </c>
@@ -32303,8 +34254,11 @@
       <c r="R533" s="2" t="s">
         <v>1338</v>
       </c>
-    </row>
-    <row r="534" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S533" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="534" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A534" s="5" t="s">
         <v>1339</v>
       </c>
@@ -32347,8 +34301,11 @@
       <c r="R534" s="2" t="s">
         <v>1343</v>
       </c>
-    </row>
-    <row r="535" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S534" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="535" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A535" s="5" t="s">
         <v>1344</v>
       </c>
@@ -32391,8 +34348,11 @@
       <c r="R535" s="2" t="s">
         <v>1349</v>
       </c>
-    </row>
-    <row r="536" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S535" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="536" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A536" s="5" t="s">
         <v>1350</v>
       </c>
@@ -32435,8 +34395,11 @@
       <c r="R536" s="2" t="s">
         <v>1349</v>
       </c>
-    </row>
-    <row r="537" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S536" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="537" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A537" s="5" t="s">
         <v>1351</v>
       </c>
@@ -32479,8 +34442,11 @@
       <c r="R537" s="2" t="s">
         <v>1355</v>
       </c>
-    </row>
-    <row r="538" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S537" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="538" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A538" s="5" t="s">
         <v>1356</v>
       </c>
@@ -32523,8 +34489,11 @@
       <c r="R538" s="2" t="s">
         <v>1355</v>
       </c>
-    </row>
-    <row r="539" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S538" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="539" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A539" s="5" t="s">
         <v>1357</v>
       </c>
@@ -32567,8 +34536,11 @@
       <c r="R539" s="2" t="s">
         <v>1363</v>
       </c>
-    </row>
-    <row r="540" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S539" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="540" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A540" s="5" t="s">
         <v>1364</v>
       </c>
@@ -32611,8 +34583,11 @@
       <c r="R540" s="2" t="s">
         <v>1370</v>
       </c>
-    </row>
-    <row r="541" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S540" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="541" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A541" s="5" t="s">
         <v>1371</v>
       </c>
@@ -32655,8 +34630,11 @@
       <c r="R541" s="2" t="s">
         <v>1376</v>
       </c>
-    </row>
-    <row r="542" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S541" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="542" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A542" s="5" t="s">
         <v>1377</v>
       </c>
@@ -32699,8 +34677,11 @@
       <c r="R542" s="2" t="s">
         <v>1376</v>
       </c>
-    </row>
-    <row r="543" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S542" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="543" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A543" s="5" t="s">
         <v>1378</v>
       </c>
@@ -32743,8 +34724,11 @@
       <c r="R543" s="2" t="s">
         <v>1376</v>
       </c>
-    </row>
-    <row r="544" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S543" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="544" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A544" s="5" t="s">
         <v>1379</v>
       </c>
@@ -32787,8 +34771,11 @@
       <c r="R544" s="2" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="545" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S544" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="545" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A545" s="5" t="s">
         <v>1385</v>
       </c>
@@ -32831,8 +34818,11 @@
       <c r="R545" s="2" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="546" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S545" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="546" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A546" s="5" t="s">
         <v>1386</v>
       </c>
@@ -32875,8 +34865,11 @@
       <c r="R546" s="2" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="547" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S546" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="547" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A547" s="5" t="s">
         <v>1391</v>
       </c>
@@ -32919,8 +34912,11 @@
       <c r="R547" s="2" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="548" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S547" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="548" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A548" s="5" t="s">
         <v>1392</v>
       </c>
@@ -32963,8 +34959,11 @@
       <c r="R548" s="2" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="549" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S548" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="549" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A549" s="5" t="s">
         <v>1393</v>
       </c>
@@ -33007,8 +35006,11 @@
       <c r="R549" s="2" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="550" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S549" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="550" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A550" s="5" t="s">
         <v>1394</v>
       </c>
@@ -33051,8 +35053,11 @@
       <c r="R550" s="2" t="s">
         <v>1399</v>
       </c>
-    </row>
-    <row r="551" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S550" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="551" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A551" s="5" t="s">
         <v>1400</v>
       </c>
@@ -33095,8 +35100,11 @@
       <c r="R551" s="2" t="s">
         <v>1405</v>
       </c>
-    </row>
-    <row r="552" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S551" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A552" s="5" t="s">
         <v>1406</v>
       </c>
@@ -33139,8 +35147,11 @@
       <c r="R552" s="2" t="s">
         <v>1411</v>
       </c>
-    </row>
-    <row r="553" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S552" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="553" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A553" s="5" t="s">
         <v>1412</v>
       </c>
@@ -33183,8 +35194,11 @@
       <c r="R553" s="2" t="s">
         <v>1418</v>
       </c>
-    </row>
-    <row r="554" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S553" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="554" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A554" s="5" t="s">
         <v>1419</v>
       </c>
@@ -33227,8 +35241,11 @@
       <c r="R554" s="2" t="s">
         <v>1423</v>
       </c>
-    </row>
-    <row r="555" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S554" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="555" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A555" s="5" t="s">
         <v>1424</v>
       </c>
@@ -33271,8 +35288,11 @@
       <c r="R555" s="2" t="s">
         <v>1429</v>
       </c>
-    </row>
-    <row r="556" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S555" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="556" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A556" s="5" t="s">
         <v>1430</v>
       </c>
@@ -33315,8 +35335,11 @@
       <c r="R556" s="2" t="s">
         <v>1435</v>
       </c>
-    </row>
-    <row r="557" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S556" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="557" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A557" s="5" t="s">
         <v>1436</v>
       </c>
@@ -33359,8 +35382,11 @@
       <c r="R557" s="2" t="s">
         <v>1441</v>
       </c>
-    </row>
-    <row r="558" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S557" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A558" s="5" t="s">
         <v>1442</v>
       </c>
@@ -33403,8 +35429,11 @@
       <c r="R558" s="2" t="s">
         <v>1448</v>
       </c>
-    </row>
-    <row r="559" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S558" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="559" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A559" s="5" t="s">
         <v>1449</v>
       </c>
@@ -33447,8 +35476,11 @@
       <c r="R559" s="2" t="s">
         <v>1453</v>
       </c>
-    </row>
-    <row r="560" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S559" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="560" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A560" s="5" t="s">
         <v>1454</v>
       </c>
@@ -33491,8 +35523,11 @@
       <c r="R560" s="2" t="s">
         <v>1459</v>
       </c>
-    </row>
-    <row r="561" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S560" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="561" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A561" s="5" t="s">
         <v>1460</v>
       </c>
@@ -33535,8 +35570,11 @@
       <c r="R561" s="2" t="s">
         <v>1464</v>
       </c>
-    </row>
-    <row r="562" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S561" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="562" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A562" s="5" t="s">
         <v>1465</v>
       </c>
@@ -33579,8 +35617,11 @@
       <c r="R562" s="2" t="s">
         <v>1468</v>
       </c>
-    </row>
-    <row r="563" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S562" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="563" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A563" s="5" t="s">
         <v>1469</v>
       </c>
@@ -33623,8 +35664,11 @@
       <c r="R563" s="2" t="s">
         <v>1468</v>
       </c>
-    </row>
-    <row r="564" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S563" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="564" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A564" s="5" t="s">
         <v>1470</v>
       </c>
@@ -33677,8 +35721,11 @@
       <c r="R564" s="2" t="s">
         <v>1478</v>
       </c>
-    </row>
-    <row r="565" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S564" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="565" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A565" s="5" t="s">
         <v>1479</v>
       </c>
@@ -33731,8 +35778,11 @@
       <c r="R565" s="2" t="s">
         <v>1478</v>
       </c>
-    </row>
-    <row r="566" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S565" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A566" s="5" t="s">
         <v>1480</v>
       </c>
@@ -33785,8 +35835,11 @@
       <c r="R566" s="2" t="s">
         <v>1478</v>
       </c>
-    </row>
-    <row r="567" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="S566" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A567" s="5" t="s">
         <v>1481</v>
       </c>
@@ -33839,9 +35892,570 @@
       <c r="R567" s="2" t="s">
         <v>1489</v>
       </c>
+      <c r="S567" t="s">
+        <v>1607</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="567">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="A147:B147"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="A150:B150"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="A154:B154"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A156:B156"/>
+    <mergeCell ref="A157:B157"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="A174:B174"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="A176:B176"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="A180:B180"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A186:B186"/>
+    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="A188:B188"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="A190:B190"/>
+    <mergeCell ref="A191:B191"/>
+    <mergeCell ref="A192:B192"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="A195:B195"/>
+    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="A197:B197"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="A200:B200"/>
+    <mergeCell ref="A201:B201"/>
+    <mergeCell ref="A202:B202"/>
+    <mergeCell ref="A203:B203"/>
+    <mergeCell ref="A204:B204"/>
+    <mergeCell ref="A205:B205"/>
+    <mergeCell ref="A206:B206"/>
+    <mergeCell ref="A207:B207"/>
+    <mergeCell ref="A208:B208"/>
+    <mergeCell ref="A209:B209"/>
+    <mergeCell ref="A210:B210"/>
+    <mergeCell ref="A211:B211"/>
+    <mergeCell ref="A212:B212"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="A215:B215"/>
+    <mergeCell ref="A216:B216"/>
+    <mergeCell ref="A217:B217"/>
+    <mergeCell ref="A218:B218"/>
+    <mergeCell ref="A219:B219"/>
+    <mergeCell ref="A220:B220"/>
+    <mergeCell ref="A221:B221"/>
+    <mergeCell ref="A222:B222"/>
+    <mergeCell ref="A223:B223"/>
+    <mergeCell ref="A224:B224"/>
+    <mergeCell ref="A225:B225"/>
+    <mergeCell ref="A226:B226"/>
+    <mergeCell ref="A227:B227"/>
+    <mergeCell ref="A228:B228"/>
+    <mergeCell ref="A229:B229"/>
+    <mergeCell ref="A230:B230"/>
+    <mergeCell ref="A231:B231"/>
+    <mergeCell ref="A232:B232"/>
+    <mergeCell ref="A233:B233"/>
+    <mergeCell ref="A234:B234"/>
+    <mergeCell ref="A235:B235"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A237:B237"/>
+    <mergeCell ref="A238:B238"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A240:B240"/>
+    <mergeCell ref="A241:B241"/>
+    <mergeCell ref="A242:B242"/>
+    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="A244:B244"/>
+    <mergeCell ref="A245:B245"/>
+    <mergeCell ref="A246:B246"/>
+    <mergeCell ref="A247:B247"/>
+    <mergeCell ref="A248:B248"/>
+    <mergeCell ref="A249:B249"/>
+    <mergeCell ref="A250:B250"/>
+    <mergeCell ref="A251:B251"/>
+    <mergeCell ref="A252:B252"/>
+    <mergeCell ref="A253:B253"/>
+    <mergeCell ref="A254:B254"/>
+    <mergeCell ref="A255:B255"/>
+    <mergeCell ref="A256:B256"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A258:B258"/>
+    <mergeCell ref="A259:B259"/>
+    <mergeCell ref="A260:B260"/>
+    <mergeCell ref="A261:B261"/>
+    <mergeCell ref="A262:B262"/>
+    <mergeCell ref="A263:B263"/>
+    <mergeCell ref="A264:B264"/>
+    <mergeCell ref="A265:B265"/>
+    <mergeCell ref="A266:B266"/>
+    <mergeCell ref="A267:B267"/>
+    <mergeCell ref="A268:B268"/>
+    <mergeCell ref="A269:B269"/>
+    <mergeCell ref="A270:B270"/>
+    <mergeCell ref="A271:B271"/>
+    <mergeCell ref="A272:B272"/>
+    <mergeCell ref="A273:B273"/>
+    <mergeCell ref="A274:B274"/>
+    <mergeCell ref="A275:B275"/>
+    <mergeCell ref="A276:B276"/>
+    <mergeCell ref="A277:B277"/>
+    <mergeCell ref="A278:B278"/>
+    <mergeCell ref="A279:B279"/>
+    <mergeCell ref="A280:B280"/>
+    <mergeCell ref="A281:B281"/>
+    <mergeCell ref="A282:B282"/>
+    <mergeCell ref="A283:B283"/>
+    <mergeCell ref="A284:B284"/>
+    <mergeCell ref="A285:B285"/>
+    <mergeCell ref="A286:B286"/>
+    <mergeCell ref="A287:B287"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A289:B289"/>
+    <mergeCell ref="A290:B290"/>
+    <mergeCell ref="A291:B291"/>
+    <mergeCell ref="A292:B292"/>
+    <mergeCell ref="A293:B293"/>
+    <mergeCell ref="A294:B294"/>
+    <mergeCell ref="A295:B295"/>
+    <mergeCell ref="A296:B296"/>
+    <mergeCell ref="A297:B297"/>
+    <mergeCell ref="A298:B298"/>
+    <mergeCell ref="A299:B299"/>
+    <mergeCell ref="A300:B300"/>
+    <mergeCell ref="A301:B301"/>
+    <mergeCell ref="A302:B302"/>
+    <mergeCell ref="A303:B303"/>
+    <mergeCell ref="A304:B304"/>
+    <mergeCell ref="A305:B305"/>
+    <mergeCell ref="A306:B306"/>
+    <mergeCell ref="A307:B307"/>
+    <mergeCell ref="A308:B308"/>
+    <mergeCell ref="A309:B309"/>
+    <mergeCell ref="A310:B310"/>
+    <mergeCell ref="A311:B311"/>
+    <mergeCell ref="A312:B312"/>
+    <mergeCell ref="A313:B313"/>
+    <mergeCell ref="A314:B314"/>
+    <mergeCell ref="A315:B315"/>
+    <mergeCell ref="A316:B316"/>
+    <mergeCell ref="A317:B317"/>
+    <mergeCell ref="A318:B318"/>
+    <mergeCell ref="A319:B319"/>
+    <mergeCell ref="A320:B320"/>
+    <mergeCell ref="A321:B321"/>
+    <mergeCell ref="A322:B322"/>
+    <mergeCell ref="A323:B323"/>
+    <mergeCell ref="A324:B324"/>
+    <mergeCell ref="A325:B325"/>
+    <mergeCell ref="A326:B326"/>
+    <mergeCell ref="A327:B327"/>
+    <mergeCell ref="A328:B328"/>
+    <mergeCell ref="A329:B329"/>
+    <mergeCell ref="A330:B330"/>
+    <mergeCell ref="A331:B331"/>
+    <mergeCell ref="A332:B332"/>
+    <mergeCell ref="A333:B333"/>
+    <mergeCell ref="A334:B334"/>
+    <mergeCell ref="A335:B335"/>
+    <mergeCell ref="A336:B336"/>
+    <mergeCell ref="A337:B337"/>
+    <mergeCell ref="A338:B338"/>
+    <mergeCell ref="A339:B339"/>
+    <mergeCell ref="A340:B340"/>
+    <mergeCell ref="A341:B341"/>
+    <mergeCell ref="A342:B342"/>
+    <mergeCell ref="A343:B343"/>
+    <mergeCell ref="A344:B344"/>
+    <mergeCell ref="A345:B345"/>
+    <mergeCell ref="A346:B346"/>
+    <mergeCell ref="A347:B347"/>
+    <mergeCell ref="A348:B348"/>
+    <mergeCell ref="A349:B349"/>
+    <mergeCell ref="A350:B350"/>
+    <mergeCell ref="A351:B351"/>
+    <mergeCell ref="A352:B352"/>
+    <mergeCell ref="A353:B353"/>
+    <mergeCell ref="A354:B354"/>
+    <mergeCell ref="A355:B355"/>
+    <mergeCell ref="A356:B356"/>
+    <mergeCell ref="A357:B357"/>
+    <mergeCell ref="A358:B358"/>
+    <mergeCell ref="A359:B359"/>
+    <mergeCell ref="A360:B360"/>
+    <mergeCell ref="A361:B361"/>
+    <mergeCell ref="A362:B362"/>
+    <mergeCell ref="A363:B363"/>
+    <mergeCell ref="A364:B364"/>
+    <mergeCell ref="A365:B365"/>
+    <mergeCell ref="A366:B366"/>
+    <mergeCell ref="A367:B367"/>
+    <mergeCell ref="A368:B368"/>
+    <mergeCell ref="A369:B369"/>
+    <mergeCell ref="A370:B370"/>
+    <mergeCell ref="A371:B371"/>
+    <mergeCell ref="A372:B372"/>
+    <mergeCell ref="A373:B373"/>
+    <mergeCell ref="A374:B374"/>
+    <mergeCell ref="A375:B375"/>
+    <mergeCell ref="A376:B376"/>
+    <mergeCell ref="A377:B377"/>
+    <mergeCell ref="A378:B378"/>
+    <mergeCell ref="A379:B379"/>
+    <mergeCell ref="A380:B380"/>
+    <mergeCell ref="A381:B381"/>
+    <mergeCell ref="A382:B382"/>
+    <mergeCell ref="A383:B383"/>
+    <mergeCell ref="A384:B384"/>
+    <mergeCell ref="A385:B385"/>
+    <mergeCell ref="A386:B386"/>
+    <mergeCell ref="A387:B387"/>
+    <mergeCell ref="A388:B388"/>
+    <mergeCell ref="A389:B389"/>
+    <mergeCell ref="A390:B390"/>
+    <mergeCell ref="A391:B391"/>
+    <mergeCell ref="A392:B392"/>
+    <mergeCell ref="A393:B393"/>
+    <mergeCell ref="A394:B394"/>
+    <mergeCell ref="A395:B395"/>
+    <mergeCell ref="A396:B396"/>
+    <mergeCell ref="A397:B397"/>
+    <mergeCell ref="A398:B398"/>
+    <mergeCell ref="A399:B399"/>
+    <mergeCell ref="A400:B400"/>
+    <mergeCell ref="A401:B401"/>
+    <mergeCell ref="A402:B402"/>
+    <mergeCell ref="A403:B403"/>
+    <mergeCell ref="A404:B404"/>
+    <mergeCell ref="A405:B405"/>
+    <mergeCell ref="A406:B406"/>
+    <mergeCell ref="A407:B407"/>
+    <mergeCell ref="A408:B408"/>
+    <mergeCell ref="A409:B409"/>
+    <mergeCell ref="A410:B410"/>
+    <mergeCell ref="A411:B411"/>
+    <mergeCell ref="A412:B412"/>
+    <mergeCell ref="A413:B413"/>
+    <mergeCell ref="A414:B414"/>
+    <mergeCell ref="A415:B415"/>
+    <mergeCell ref="A416:B416"/>
+    <mergeCell ref="A417:B417"/>
+    <mergeCell ref="A418:B418"/>
+    <mergeCell ref="A419:B419"/>
+    <mergeCell ref="A420:B420"/>
+    <mergeCell ref="A421:B421"/>
+    <mergeCell ref="A422:B422"/>
+    <mergeCell ref="A423:B423"/>
+    <mergeCell ref="A424:B424"/>
+    <mergeCell ref="A425:B425"/>
+    <mergeCell ref="A426:B426"/>
+    <mergeCell ref="A427:B427"/>
+    <mergeCell ref="A428:B428"/>
+    <mergeCell ref="A429:B429"/>
+    <mergeCell ref="A430:B430"/>
+    <mergeCell ref="A431:B431"/>
+    <mergeCell ref="A432:B432"/>
+    <mergeCell ref="A433:B433"/>
+    <mergeCell ref="A434:B434"/>
+    <mergeCell ref="A435:B435"/>
+    <mergeCell ref="A436:B436"/>
+    <mergeCell ref="A437:B437"/>
+    <mergeCell ref="A438:B438"/>
+    <mergeCell ref="A439:B439"/>
+    <mergeCell ref="A440:B440"/>
+    <mergeCell ref="A441:B441"/>
+    <mergeCell ref="A442:B442"/>
+    <mergeCell ref="A443:B443"/>
+    <mergeCell ref="A444:B444"/>
+    <mergeCell ref="A445:B445"/>
+    <mergeCell ref="A446:B446"/>
+    <mergeCell ref="A447:B447"/>
+    <mergeCell ref="A448:B448"/>
+    <mergeCell ref="A449:B449"/>
+    <mergeCell ref="A450:B450"/>
+    <mergeCell ref="A451:B451"/>
+    <mergeCell ref="A452:B452"/>
+    <mergeCell ref="A453:B453"/>
+    <mergeCell ref="A454:B454"/>
+    <mergeCell ref="A455:B455"/>
+    <mergeCell ref="A456:B456"/>
+    <mergeCell ref="A457:B457"/>
+    <mergeCell ref="A458:B458"/>
+    <mergeCell ref="A459:B459"/>
+    <mergeCell ref="A460:B460"/>
+    <mergeCell ref="A461:B461"/>
+    <mergeCell ref="A462:B462"/>
+    <mergeCell ref="A463:B463"/>
+    <mergeCell ref="A464:B464"/>
+    <mergeCell ref="A465:B465"/>
+    <mergeCell ref="A466:B466"/>
+    <mergeCell ref="A467:B467"/>
+    <mergeCell ref="A468:B468"/>
+    <mergeCell ref="A469:B469"/>
+    <mergeCell ref="A470:B470"/>
+    <mergeCell ref="A471:B471"/>
+    <mergeCell ref="A472:B472"/>
+    <mergeCell ref="A473:B473"/>
+    <mergeCell ref="A474:B474"/>
+    <mergeCell ref="A475:B475"/>
+    <mergeCell ref="A476:B476"/>
+    <mergeCell ref="A477:B477"/>
+    <mergeCell ref="A478:B478"/>
+    <mergeCell ref="A479:B479"/>
+    <mergeCell ref="A480:B480"/>
+    <mergeCell ref="A481:B481"/>
+    <mergeCell ref="A482:B482"/>
+    <mergeCell ref="A483:B483"/>
+    <mergeCell ref="A484:B484"/>
+    <mergeCell ref="A485:B485"/>
+    <mergeCell ref="A486:B486"/>
+    <mergeCell ref="A487:B487"/>
+    <mergeCell ref="A488:B488"/>
+    <mergeCell ref="A489:B489"/>
+    <mergeCell ref="A490:B490"/>
+    <mergeCell ref="A491:B491"/>
+    <mergeCell ref="A492:B492"/>
+    <mergeCell ref="A493:B493"/>
+    <mergeCell ref="A494:B494"/>
+    <mergeCell ref="A495:B495"/>
+    <mergeCell ref="A496:B496"/>
+    <mergeCell ref="A497:B497"/>
+    <mergeCell ref="A498:B498"/>
+    <mergeCell ref="A499:B499"/>
+    <mergeCell ref="A500:B500"/>
+    <mergeCell ref="A501:B501"/>
+    <mergeCell ref="A502:B502"/>
+    <mergeCell ref="A503:B503"/>
+    <mergeCell ref="A504:B504"/>
+    <mergeCell ref="A505:B505"/>
+    <mergeCell ref="A506:B506"/>
+    <mergeCell ref="A507:B507"/>
+    <mergeCell ref="A508:B508"/>
+    <mergeCell ref="A509:B509"/>
+    <mergeCell ref="A510:B510"/>
+    <mergeCell ref="A511:B511"/>
+    <mergeCell ref="A512:B512"/>
+    <mergeCell ref="A513:B513"/>
+    <mergeCell ref="A514:B514"/>
+    <mergeCell ref="A515:B515"/>
+    <mergeCell ref="A516:B516"/>
+    <mergeCell ref="A517:B517"/>
+    <mergeCell ref="A518:B518"/>
+    <mergeCell ref="A519:B519"/>
+    <mergeCell ref="A520:B520"/>
+    <mergeCell ref="A521:B521"/>
+    <mergeCell ref="A522:B522"/>
+    <mergeCell ref="A523:B523"/>
+    <mergeCell ref="A524:B524"/>
+    <mergeCell ref="A525:B525"/>
+    <mergeCell ref="A526:B526"/>
+    <mergeCell ref="A527:B527"/>
+    <mergeCell ref="A528:B528"/>
+    <mergeCell ref="A529:B529"/>
+    <mergeCell ref="A530:B530"/>
+    <mergeCell ref="A531:B531"/>
+    <mergeCell ref="A532:B532"/>
+    <mergeCell ref="A533:B533"/>
+    <mergeCell ref="A534:B534"/>
+    <mergeCell ref="A535:B535"/>
+    <mergeCell ref="A536:B536"/>
+    <mergeCell ref="A537:B537"/>
+    <mergeCell ref="A538:B538"/>
+    <mergeCell ref="A539:B539"/>
+    <mergeCell ref="A540:B540"/>
+    <mergeCell ref="A541:B541"/>
+    <mergeCell ref="A542:B542"/>
+    <mergeCell ref="A543:B543"/>
+    <mergeCell ref="A544:B544"/>
+    <mergeCell ref="A545:B545"/>
+    <mergeCell ref="A546:B546"/>
+    <mergeCell ref="A547:B547"/>
+    <mergeCell ref="A548:B548"/>
+    <mergeCell ref="A549:B549"/>
+    <mergeCell ref="A550:B550"/>
+    <mergeCell ref="A551:B551"/>
+    <mergeCell ref="A552:B552"/>
+    <mergeCell ref="A553:B553"/>
+    <mergeCell ref="A554:B554"/>
+    <mergeCell ref="A555:B555"/>
+    <mergeCell ref="A556:B556"/>
+    <mergeCell ref="A557:B557"/>
+    <mergeCell ref="A558:B558"/>
     <mergeCell ref="A559:B559"/>
     <mergeCell ref="A560:B560"/>
     <mergeCell ref="A561:B561"/>
@@ -33851,564 +36465,6 @@
     <mergeCell ref="A565:B565"/>
     <mergeCell ref="A566:B566"/>
     <mergeCell ref="A567:B567"/>
-    <mergeCell ref="A550:B550"/>
-    <mergeCell ref="A551:B551"/>
-    <mergeCell ref="A552:B552"/>
-    <mergeCell ref="A553:B553"/>
-    <mergeCell ref="A554:B554"/>
-    <mergeCell ref="A555:B555"/>
-    <mergeCell ref="A556:B556"/>
-    <mergeCell ref="A557:B557"/>
-    <mergeCell ref="A558:B558"/>
-    <mergeCell ref="A541:B541"/>
-    <mergeCell ref="A542:B542"/>
-    <mergeCell ref="A543:B543"/>
-    <mergeCell ref="A544:B544"/>
-    <mergeCell ref="A545:B545"/>
-    <mergeCell ref="A546:B546"/>
-    <mergeCell ref="A547:B547"/>
-    <mergeCell ref="A548:B548"/>
-    <mergeCell ref="A549:B549"/>
-    <mergeCell ref="A532:B532"/>
-    <mergeCell ref="A533:B533"/>
-    <mergeCell ref="A534:B534"/>
-    <mergeCell ref="A535:B535"/>
-    <mergeCell ref="A536:B536"/>
-    <mergeCell ref="A537:B537"/>
-    <mergeCell ref="A538:B538"/>
-    <mergeCell ref="A539:B539"/>
-    <mergeCell ref="A540:B540"/>
-    <mergeCell ref="A523:B523"/>
-    <mergeCell ref="A524:B524"/>
-    <mergeCell ref="A525:B525"/>
-    <mergeCell ref="A526:B526"/>
-    <mergeCell ref="A527:B527"/>
-    <mergeCell ref="A528:B528"/>
-    <mergeCell ref="A529:B529"/>
-    <mergeCell ref="A530:B530"/>
-    <mergeCell ref="A531:B531"/>
-    <mergeCell ref="A514:B514"/>
-    <mergeCell ref="A515:B515"/>
-    <mergeCell ref="A516:B516"/>
-    <mergeCell ref="A517:B517"/>
-    <mergeCell ref="A518:B518"/>
-    <mergeCell ref="A519:B519"/>
-    <mergeCell ref="A520:B520"/>
-    <mergeCell ref="A521:B521"/>
-    <mergeCell ref="A522:B522"/>
-    <mergeCell ref="A505:B505"/>
-    <mergeCell ref="A506:B506"/>
-    <mergeCell ref="A507:B507"/>
-    <mergeCell ref="A508:B508"/>
-    <mergeCell ref="A509:B509"/>
-    <mergeCell ref="A510:B510"/>
-    <mergeCell ref="A511:B511"/>
-    <mergeCell ref="A512:B512"/>
-    <mergeCell ref="A513:B513"/>
-    <mergeCell ref="A496:B496"/>
-    <mergeCell ref="A497:B497"/>
-    <mergeCell ref="A498:B498"/>
-    <mergeCell ref="A499:B499"/>
-    <mergeCell ref="A500:B500"/>
-    <mergeCell ref="A501:B501"/>
-    <mergeCell ref="A502:B502"/>
-    <mergeCell ref="A503:B503"/>
-    <mergeCell ref="A504:B504"/>
-    <mergeCell ref="A487:B487"/>
-    <mergeCell ref="A488:B488"/>
-    <mergeCell ref="A489:B489"/>
-    <mergeCell ref="A490:B490"/>
-    <mergeCell ref="A491:B491"/>
-    <mergeCell ref="A492:B492"/>
-    <mergeCell ref="A493:B493"/>
-    <mergeCell ref="A494:B494"/>
-    <mergeCell ref="A495:B495"/>
-    <mergeCell ref="A478:B478"/>
-    <mergeCell ref="A479:B479"/>
-    <mergeCell ref="A480:B480"/>
-    <mergeCell ref="A481:B481"/>
-    <mergeCell ref="A482:B482"/>
-    <mergeCell ref="A483:B483"/>
-    <mergeCell ref="A484:B484"/>
-    <mergeCell ref="A485:B485"/>
-    <mergeCell ref="A486:B486"/>
-    <mergeCell ref="A469:B469"/>
-    <mergeCell ref="A470:B470"/>
-    <mergeCell ref="A471:B471"/>
-    <mergeCell ref="A472:B472"/>
-    <mergeCell ref="A473:B473"/>
-    <mergeCell ref="A474:B474"/>
-    <mergeCell ref="A475:B475"/>
-    <mergeCell ref="A476:B476"/>
-    <mergeCell ref="A477:B477"/>
-    <mergeCell ref="A460:B460"/>
-    <mergeCell ref="A461:B461"/>
-    <mergeCell ref="A462:B462"/>
-    <mergeCell ref="A463:B463"/>
-    <mergeCell ref="A464:B464"/>
-    <mergeCell ref="A465:B465"/>
-    <mergeCell ref="A466:B466"/>
-    <mergeCell ref="A467:B467"/>
-    <mergeCell ref="A468:B468"/>
-    <mergeCell ref="A451:B451"/>
-    <mergeCell ref="A452:B452"/>
-    <mergeCell ref="A453:B453"/>
-    <mergeCell ref="A454:B454"/>
-    <mergeCell ref="A455:B455"/>
-    <mergeCell ref="A456:B456"/>
-    <mergeCell ref="A457:B457"/>
-    <mergeCell ref="A458:B458"/>
-    <mergeCell ref="A459:B459"/>
-    <mergeCell ref="A442:B442"/>
-    <mergeCell ref="A443:B443"/>
-    <mergeCell ref="A444:B444"/>
-    <mergeCell ref="A445:B445"/>
-    <mergeCell ref="A446:B446"/>
-    <mergeCell ref="A447:B447"/>
-    <mergeCell ref="A448:B448"/>
-    <mergeCell ref="A449:B449"/>
-    <mergeCell ref="A450:B450"/>
-    <mergeCell ref="A433:B433"/>
-    <mergeCell ref="A434:B434"/>
-    <mergeCell ref="A435:B435"/>
-    <mergeCell ref="A436:B436"/>
-    <mergeCell ref="A437:B437"/>
-    <mergeCell ref="A438:B438"/>
-    <mergeCell ref="A439:B439"/>
-    <mergeCell ref="A440:B440"/>
-    <mergeCell ref="A441:B441"/>
-    <mergeCell ref="A424:B424"/>
-    <mergeCell ref="A425:B425"/>
-    <mergeCell ref="A426:B426"/>
-    <mergeCell ref="A427:B427"/>
-    <mergeCell ref="A428:B428"/>
-    <mergeCell ref="A429:B429"/>
-    <mergeCell ref="A430:B430"/>
-    <mergeCell ref="A431:B431"/>
-    <mergeCell ref="A432:B432"/>
-    <mergeCell ref="A415:B415"/>
-    <mergeCell ref="A416:B416"/>
-    <mergeCell ref="A417:B417"/>
-    <mergeCell ref="A418:B418"/>
-    <mergeCell ref="A419:B419"/>
-    <mergeCell ref="A420:B420"/>
-    <mergeCell ref="A421:B421"/>
-    <mergeCell ref="A422:B422"/>
-    <mergeCell ref="A423:B423"/>
-    <mergeCell ref="A406:B406"/>
-    <mergeCell ref="A407:B407"/>
-    <mergeCell ref="A408:B408"/>
-    <mergeCell ref="A409:B409"/>
-    <mergeCell ref="A410:B410"/>
-    <mergeCell ref="A411:B411"/>
-    <mergeCell ref="A412:B412"/>
-    <mergeCell ref="A413:B413"/>
-    <mergeCell ref="A414:B414"/>
-    <mergeCell ref="A397:B397"/>
-    <mergeCell ref="A398:B398"/>
-    <mergeCell ref="A399:B399"/>
-    <mergeCell ref="A400:B400"/>
-    <mergeCell ref="A401:B401"/>
-    <mergeCell ref="A402:B402"/>
-    <mergeCell ref="A403:B403"/>
-    <mergeCell ref="A404:B404"/>
-    <mergeCell ref="A405:B405"/>
-    <mergeCell ref="A388:B388"/>
-    <mergeCell ref="A389:B389"/>
-    <mergeCell ref="A390:B390"/>
-    <mergeCell ref="A391:B391"/>
-    <mergeCell ref="A392:B392"/>
-    <mergeCell ref="A393:B393"/>
-    <mergeCell ref="A394:B394"/>
-    <mergeCell ref="A395:B395"/>
-    <mergeCell ref="A396:B396"/>
-    <mergeCell ref="A379:B379"/>
-    <mergeCell ref="A380:B380"/>
-    <mergeCell ref="A381:B381"/>
-    <mergeCell ref="A382:B382"/>
-    <mergeCell ref="A383:B383"/>
-    <mergeCell ref="A384:B384"/>
-    <mergeCell ref="A385:B385"/>
-    <mergeCell ref="A386:B386"/>
-    <mergeCell ref="A387:B387"/>
-    <mergeCell ref="A370:B370"/>
-    <mergeCell ref="A371:B371"/>
-    <mergeCell ref="A372:B372"/>
-    <mergeCell ref="A373:B373"/>
-    <mergeCell ref="A374:B374"/>
-    <mergeCell ref="A375:B375"/>
-    <mergeCell ref="A376:B376"/>
-    <mergeCell ref="A377:B377"/>
-    <mergeCell ref="A378:B378"/>
-    <mergeCell ref="A361:B361"/>
-    <mergeCell ref="A362:B362"/>
-    <mergeCell ref="A363:B363"/>
-    <mergeCell ref="A364:B364"/>
-    <mergeCell ref="A365:B365"/>
-    <mergeCell ref="A366:B366"/>
-    <mergeCell ref="A367:B367"/>
-    <mergeCell ref="A368:B368"/>
-    <mergeCell ref="A369:B369"/>
-    <mergeCell ref="A352:B352"/>
-    <mergeCell ref="A353:B353"/>
-    <mergeCell ref="A354:B354"/>
-    <mergeCell ref="A355:B355"/>
-    <mergeCell ref="A356:B356"/>
-    <mergeCell ref="A357:B357"/>
-    <mergeCell ref="A358:B358"/>
-    <mergeCell ref="A359:B359"/>
-    <mergeCell ref="A360:B360"/>
-    <mergeCell ref="A343:B343"/>
-    <mergeCell ref="A344:B344"/>
-    <mergeCell ref="A345:B345"/>
-    <mergeCell ref="A346:B346"/>
-    <mergeCell ref="A347:B347"/>
-    <mergeCell ref="A348:B348"/>
-    <mergeCell ref="A349:B349"/>
-    <mergeCell ref="A350:B350"/>
-    <mergeCell ref="A351:B351"/>
-    <mergeCell ref="A334:B334"/>
-    <mergeCell ref="A335:B335"/>
-    <mergeCell ref="A336:B336"/>
-    <mergeCell ref="A337:B337"/>
-    <mergeCell ref="A338:B338"/>
-    <mergeCell ref="A339:B339"/>
-    <mergeCell ref="A340:B340"/>
-    <mergeCell ref="A341:B341"/>
-    <mergeCell ref="A342:B342"/>
-    <mergeCell ref="A325:B325"/>
-    <mergeCell ref="A326:B326"/>
-    <mergeCell ref="A327:B327"/>
-    <mergeCell ref="A328:B328"/>
-    <mergeCell ref="A329:B329"/>
-    <mergeCell ref="A330:B330"/>
-    <mergeCell ref="A331:B331"/>
-    <mergeCell ref="A332:B332"/>
-    <mergeCell ref="A333:B333"/>
-    <mergeCell ref="A316:B316"/>
-    <mergeCell ref="A317:B317"/>
-    <mergeCell ref="A318:B318"/>
-    <mergeCell ref="A319:B319"/>
-    <mergeCell ref="A320:B320"/>
-    <mergeCell ref="A321:B321"/>
-    <mergeCell ref="A322:B322"/>
-    <mergeCell ref="A323:B323"/>
-    <mergeCell ref="A324:B324"/>
-    <mergeCell ref="A307:B307"/>
-    <mergeCell ref="A308:B308"/>
-    <mergeCell ref="A309:B309"/>
-    <mergeCell ref="A310:B310"/>
-    <mergeCell ref="A311:B311"/>
-    <mergeCell ref="A312:B312"/>
-    <mergeCell ref="A313:B313"/>
-    <mergeCell ref="A314:B314"/>
-    <mergeCell ref="A315:B315"/>
-    <mergeCell ref="A298:B298"/>
-    <mergeCell ref="A299:B299"/>
-    <mergeCell ref="A300:B300"/>
-    <mergeCell ref="A301:B301"/>
-    <mergeCell ref="A302:B302"/>
-    <mergeCell ref="A303:B303"/>
-    <mergeCell ref="A304:B304"/>
-    <mergeCell ref="A305:B305"/>
-    <mergeCell ref="A306:B306"/>
-    <mergeCell ref="A289:B289"/>
-    <mergeCell ref="A290:B290"/>
-    <mergeCell ref="A291:B291"/>
-    <mergeCell ref="A292:B292"/>
-    <mergeCell ref="A293:B293"/>
-    <mergeCell ref="A294:B294"/>
-    <mergeCell ref="A295:B295"/>
-    <mergeCell ref="A296:B296"/>
-    <mergeCell ref="A297:B297"/>
-    <mergeCell ref="A280:B280"/>
-    <mergeCell ref="A281:B281"/>
-    <mergeCell ref="A282:B282"/>
-    <mergeCell ref="A283:B283"/>
-    <mergeCell ref="A284:B284"/>
-    <mergeCell ref="A285:B285"/>
-    <mergeCell ref="A286:B286"/>
-    <mergeCell ref="A287:B287"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A271:B271"/>
-    <mergeCell ref="A272:B272"/>
-    <mergeCell ref="A273:B273"/>
-    <mergeCell ref="A274:B274"/>
-    <mergeCell ref="A275:B275"/>
-    <mergeCell ref="A276:B276"/>
-    <mergeCell ref="A277:B277"/>
-    <mergeCell ref="A278:B278"/>
-    <mergeCell ref="A279:B279"/>
-    <mergeCell ref="A262:B262"/>
-    <mergeCell ref="A263:B263"/>
-    <mergeCell ref="A264:B264"/>
-    <mergeCell ref="A265:B265"/>
-    <mergeCell ref="A266:B266"/>
-    <mergeCell ref="A267:B267"/>
-    <mergeCell ref="A268:B268"/>
-    <mergeCell ref="A269:B269"/>
-    <mergeCell ref="A270:B270"/>
-    <mergeCell ref="A253:B253"/>
-    <mergeCell ref="A254:B254"/>
-    <mergeCell ref="A255:B255"/>
-    <mergeCell ref="A256:B256"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A258:B258"/>
-    <mergeCell ref="A259:B259"/>
-    <mergeCell ref="A260:B260"/>
-    <mergeCell ref="A261:B261"/>
-    <mergeCell ref="A244:B244"/>
-    <mergeCell ref="A245:B245"/>
-    <mergeCell ref="A246:B246"/>
-    <mergeCell ref="A247:B247"/>
-    <mergeCell ref="A248:B248"/>
-    <mergeCell ref="A249:B249"/>
-    <mergeCell ref="A250:B250"/>
-    <mergeCell ref="A251:B251"/>
-    <mergeCell ref="A252:B252"/>
-    <mergeCell ref="A235:B235"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A237:B237"/>
-    <mergeCell ref="A238:B238"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A240:B240"/>
-    <mergeCell ref="A241:B241"/>
-    <mergeCell ref="A242:B242"/>
-    <mergeCell ref="A243:B243"/>
-    <mergeCell ref="A226:B226"/>
-    <mergeCell ref="A227:B227"/>
-    <mergeCell ref="A228:B228"/>
-    <mergeCell ref="A229:B229"/>
-    <mergeCell ref="A230:B230"/>
-    <mergeCell ref="A231:B231"/>
-    <mergeCell ref="A232:B232"/>
-    <mergeCell ref="A233:B233"/>
-    <mergeCell ref="A234:B234"/>
-    <mergeCell ref="A217:B217"/>
-    <mergeCell ref="A218:B218"/>
-    <mergeCell ref="A219:B219"/>
-    <mergeCell ref="A220:B220"/>
-    <mergeCell ref="A221:B221"/>
-    <mergeCell ref="A222:B222"/>
-    <mergeCell ref="A223:B223"/>
-    <mergeCell ref="A224:B224"/>
-    <mergeCell ref="A225:B225"/>
-    <mergeCell ref="A208:B208"/>
-    <mergeCell ref="A209:B209"/>
-    <mergeCell ref="A210:B210"/>
-    <mergeCell ref="A211:B211"/>
-    <mergeCell ref="A212:B212"/>
-    <mergeCell ref="A213:B213"/>
-    <mergeCell ref="A214:B214"/>
-    <mergeCell ref="A215:B215"/>
-    <mergeCell ref="A216:B216"/>
-    <mergeCell ref="A199:B199"/>
-    <mergeCell ref="A200:B200"/>
-    <mergeCell ref="A201:B201"/>
-    <mergeCell ref="A202:B202"/>
-    <mergeCell ref="A203:B203"/>
-    <mergeCell ref="A204:B204"/>
-    <mergeCell ref="A205:B205"/>
-    <mergeCell ref="A206:B206"/>
-    <mergeCell ref="A207:B207"/>
-    <mergeCell ref="A190:B190"/>
-    <mergeCell ref="A191:B191"/>
-    <mergeCell ref="A192:B192"/>
-    <mergeCell ref="A193:B193"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="A195:B195"/>
-    <mergeCell ref="A196:B196"/>
-    <mergeCell ref="A197:B197"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="A182:B182"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="A185:B185"/>
-    <mergeCell ref="A186:B186"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="A188:B188"/>
-    <mergeCell ref="A189:B189"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="A174:B174"/>
-    <mergeCell ref="A175:B175"/>
-    <mergeCell ref="A176:B176"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A164:B164"/>
-    <mergeCell ref="A165:B165"/>
-    <mergeCell ref="A166:B166"/>
-    <mergeCell ref="A167:B167"/>
-    <mergeCell ref="A168:B168"/>
-    <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="A157:B157"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="A146:B146"/>
-    <mergeCell ref="A147:B147"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A149:B149"/>
-    <mergeCell ref="A150:B150"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="A152:B152"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A112:B112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
